--- a/三端需求功能清单.xlsx
+++ b/三端需求功能清单.xlsx
@@ -13,7 +13,7 @@
     <sheet name="运营端功能清单" sheetId="4" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">宠物主端功能清单!$A$1:$I$61</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">宠物主端功能清单!$A$1:$I$64</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="684" uniqueCount="404">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="643" uniqueCount="403">
   <si>
     <t>数心智能宠物健康平台</t>
   </si>
@@ -200,559 +200,556 @@
     <t>Tab 切换「密码登录 / 验证码登录」；账号 + 密码（可切换明文/密文）提交登录；校验账号角色与入口一致，不匹配提示「该账号不属于当前入口」</t>
   </si>
   <si>
+    <t>V1.0</t>
+  </si>
+  <si>
+    <t>支持账号/手机号/邮箱登录</t>
+  </si>
+  <si>
+    <t>验证码登录</t>
+  </si>
+  <si>
+    <t>联系类型 Tab（手机号 / 邮箱）+ 国际区号选择（action-sheet）；6 位验证码 + 获取验证码倒计时</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>记住我</t>
+  </si>
+  <si>
+    <t>勾选后登录态写入 localStorage（跨会话），否则仅 sessionStorage</t>
+  </si>
+  <si>
+    <t>sp_token / sp_role</t>
+  </si>
+  <si>
+    <t>协议勾选</t>
+  </si>
+  <si>
+    <t>服务协议 + 隐私政策链接（可查看详情），勾选后方可提交</t>
+  </si>
+  <si>
+    <t>Agreement.vue</t>
+  </si>
+  <si>
+    <t>第三方登录</t>
+  </si>
+  <si>
+    <t>Google / Apple 登录按钮</t>
+  </si>
+  <si>
+    <t>演示账号一键登录</t>
+  </si>
+  <si>
+    <t>本端演示账号卡片（user/123456）一键填充</t>
+  </si>
+  <si>
+    <t>注册页</t>
+  </si>
+  <si>
+    <t>手机号/邮箱注册</t>
+  </si>
+  <si>
+    <t>联系类型 Tab + 区号选择；验证码获取（60s 倒计时）；密码 + 确认密码（明文切换）；协议勾选；注册成功回登录页预填账号</t>
+  </si>
+  <si>
+    <t>角色强绑定 user</t>
+  </si>
+  <si>
+    <t>找回密码页</t>
+  </si>
+  <si>
+    <t>重置密码</t>
+  </si>
+  <si>
+    <t>手机号/邮箱 + 验证码（scene=reset）+ 新密码 + 确认新密码；成功回登录页预填账号</t>
+  </si>
+  <si>
+    <t>首页</t>
+  </si>
+  <si>
+    <t>宠物切换条</t>
+  </si>
+  <si>
+    <t>宠物切换与添加</t>
+  </si>
+  <si>
+    <t>顶部横向头像栏展示名下宠物（最多 3 只），点击切换当前宠物；末尾「+」跳转添加宠物；无宠物展示空态引导</t>
+  </si>
+  <si>
+    <t>宠物健康卡片</t>
+  </si>
+  <si>
+    <t>健康概览 Hero 卡片</t>
+  </si>
+  <si>
+    <t>物种图标 + 宠物名、性别、年龄、品种、体重(kg)、洗澡/驱虫/疫苗计数；点击进入宠物档案</t>
+  </si>
+  <si>
+    <t>功能模块宫格</t>
+  </si>
+  <si>
+    <t>宠物相册</t>
+  </si>
+  <si>
+    <t>2×2 宫格入口，跳转相册页</t>
+  </si>
+  <si>
+    <t>FeaturePlaceholder</t>
+  </si>
+  <si>
+    <t>待办记录</t>
+  </si>
+  <si>
+    <t>宫格入口，跳转待办页</t>
+  </si>
+  <si>
+    <t>底部快捷操作栏</t>
+  </si>
+  <si>
+    <t>在线问诊</t>
+  </si>
+  <si>
+    <t>智能助手</t>
+  </si>
+  <si>
+    <t>爱宠食谱</t>
+  </si>
+  <si>
+    <t>宠语翻译</t>
+  </si>
+  <si>
+    <t>健康自检</t>
+  </si>
+  <si>
+    <t>汉堡菜单</t>
+  </si>
+  <si>
+    <t>多宠物切换</t>
+  </si>
+  <si>
+    <t>右上角汉堡菜单支持语言切换与宠物管理入口</t>
+  </si>
+  <si>
+    <t>守护/健康监测</t>
+  </si>
+  <si>
+    <t>守护页 Health.vue</t>
+  </si>
+  <si>
+    <t>地图与轨迹展示</t>
+  </si>
+  <si>
+    <t>全屏高德地图展示宠物当前轨迹连线 + 电子围栏范围；宠物 Tab 切换监测对象</t>
+  </si>
+  <si>
+    <t>Amap 组件</t>
+  </si>
+  <si>
+    <t>守护页</t>
+  </si>
+  <si>
+    <t>宠物头部信息</t>
+  </si>
+  <si>
+    <t>宠物头像 / 名称 / 项圈设备名 / 设备状态标签（在线/离线/低电量/未绑定）/ 电量百分比 / 位置地址 + 围栏内外标注</t>
+  </si>
+  <si>
+    <t>健康指标（5 项）</t>
+  </si>
+  <si>
+    <t>体温 / 心率 / 血氧 / 呼吸 / 卡路里 实时卡片，点击进入体征详情页</t>
+  </si>
+  <si>
+    <t>VitalDetail</t>
+  </si>
+  <si>
+    <t>运动指标（4 项）</t>
+  </si>
+  <si>
+    <t>步频 / 步幅 / 步态 / 速度 实时卡片，「运动趋势」跳转</t>
+  </si>
+  <si>
+    <t>运动趋势占位</t>
+  </si>
+  <si>
+    <t>电子围栏入口</t>
+  </si>
+  <si>
+    <t>快捷工具入口，带固定围栏数量角标，跳转围栏管理</t>
+  </si>
+  <si>
+    <t>语音对讲</t>
+  </si>
+  <si>
+    <t>按住说话（MediaRecorder 录音）、上滑取消、模拟对方回复（speechSynthesis 语音播报）</t>
+  </si>
+  <si>
+    <t>远程指令</t>
+  </si>
+  <si>
+    <t>指令面板：响铃(find)/警示灯(light)/请求定位(refresh)；设备离线时禁用并提示</t>
+  </si>
+  <si>
+    <t>commandDeviceApi</t>
+  </si>
+  <si>
+    <t>体征详情页</t>
+  </si>
+  <si>
+    <t>指标切换与周期选择</t>
+  </si>
+  <si>
+    <t>体温/血氧/心率/呼吸/卡路里 5 指标 Tab；周期：单日/本周/本月/本季度（1/7/30/90 天）；单日仅当天有数据</t>
+  </si>
+  <si>
+    <t>趋势图与健康分析</t>
+  </si>
+  <si>
+    <t>趋势图按健康等级着色（正常绿/预警橙/危险红）；周期四指标分析报告（均值/最值/健康等级/建议/整体结论），分级阈值按犬/猫区分</t>
+  </si>
+  <si>
+    <t>VitalDetailChart</t>
+  </si>
+  <si>
+    <t>位置与轨迹</t>
+  </si>
+  <si>
+    <t>轨迹查看页</t>
+  </si>
+  <si>
+    <t>时间范围选择</t>
+  </si>
+  <si>
+    <t>今天 / 近 3 天 / 近 7 天 / 自定义（van-calendar，最小 30 天前）</t>
+  </si>
+  <si>
+    <t>轨迹展示</t>
+  </si>
+  <si>
+    <t>高德地图轨迹点连线，抽稀最多 150 点保证性能</t>
+  </si>
+  <si>
+    <t>轨迹汇总</t>
+  </si>
+  <si>
+    <t>宠物头像 / 名称 / 时间范围文案 / 轨迹点数 / 总里程（haversine 距离累加）；无轨迹空态</t>
+  </si>
+  <si>
+    <t>电子围栏</t>
+  </si>
+  <si>
+    <t>围栏管理页</t>
+  </si>
+  <si>
+    <t>动态围栏（跟随手机）</t>
+  </si>
+  <si>
+    <t>启用开关；距手机距离 + 围栏内/外/已关闭状态；半径滑杆（100-3000m，步长 50）+ 快捷预设（200/500/800/1500m）</t>
+  </si>
+  <si>
+    <t>仅一条</t>
+  </si>
+  <si>
+    <t>固定围栏列表</t>
+  </si>
+  <si>
+    <t>围栏名称 / 启用开关 / 半径 / 物理地址 / 编辑 / 删除（二次确认）</t>
+  </si>
+  <si>
+    <t>地址前端生成</t>
+  </si>
+  <si>
+    <t>新增固定围栏</t>
+  </si>
+  <si>
+    <t>地图选点（拖动/点击选中心点）→ 表单：名称(maxlength 20)/坐标展示/重新选点/半径滑杆/保存</t>
+  </si>
+  <si>
+    <t>增删改真实生效</t>
+  </si>
+  <si>
+    <t>宠圈社区</t>
+  </si>
+  <si>
+    <t>社区首页</t>
+  </si>
+  <si>
+    <t>信息流与搜索</t>
+  </si>
+  <si>
+    <t>按 caption / 宠物名 / 作者名 关键字搜索；宠物圈 / 关注萌宠 双 Tab；van-list 无限滚动分页</t>
+  </si>
+  <si>
+    <t>帖子卡片</t>
+  </si>
+  <si>
+    <t>作者头像/名/会员等级标签/相对时间；关注/已关注切换（取关实时移除）；文案/图片（最多 3 张 +N 角标）；浏览/点赞（橙色高亮）/评论数</t>
+  </si>
+  <si>
+    <t>帖子详情页</t>
+  </si>
+  <si>
+    <t>详情与评论</t>
+  </si>
+  <si>
+    <t>全部图片 2 列网格；关注/点赞切换；评论列表 + 底部评论栏（发送，回车提交，评论数 +1）</t>
+  </si>
+  <si>
+    <t>医生列表页</t>
+  </si>
+  <si>
+    <t>搜索与科室筛选</t>
+  </si>
+  <si>
+    <t>按姓名/医院搜索；科室分类：口腔 / 眼科 / 内科 切换</t>
+  </si>
+  <si>
+    <t>医生卡片与发起</t>
+  </si>
+  <si>
+    <t>头像/姓名/职称/医院·科室/咨询价（¥）/「马上咨询」→ 选择宠物 → 跳发起问诊；无宠物提示并引导绑定</t>
+  </si>
+  <si>
+    <t>发起问诊页</t>
+  </si>
+  <si>
+    <t>咨询内容与图片</t>
+  </si>
+  <si>
+    <t>医生信息卡 + 宠物信息卡；病情描述（必填 maxlength 500 字数统计）；图片上传最多 6 张单张 ≤5MB</t>
+  </si>
+  <si>
+    <t>健康/运动快照</t>
+  </si>
+  <si>
+    <t>只读推送近期待检体征快照（体温/心率/血氧/呼吸/卡路里/活动度/睡眠）+ 运动快照（步频/步幅/步态/速度）</t>
+  </si>
+  <si>
+    <t>问诊记录页</t>
+  </si>
+  <si>
+    <t>记录列表</t>
+  </si>
+  <si>
+    <t>宠物头像/名、医生姓名·发起时间、状态标签（进行中/已结束）、病情描述 2 行截断、最新回复预览或等待回复；右下角悬浮问诊按钮</t>
+  </si>
+  <si>
+    <t>问诊详情页</t>
+  </si>
+  <si>
+    <t>详情与医生回复</t>
+  </si>
+  <si>
+    <t>状态/发起时间；医生卡、宠物卡、病情描述、图片大图预览；健康/运动快照；医生回复卡片 + 推荐用药（名称+用法用量）/无用药建议；等待中闪烁提示</t>
+  </si>
+  <si>
+    <t>设备管理</t>
+  </si>
+  <si>
+    <t>设备列表页</t>
+  </si>
+  <si>
+    <t>设备卡片与操作</t>
+  </si>
+  <si>
+    <t>设备总数 + 绑定按钮；卡片含名称/状态标签/SN/低电量红标/电量进度条/固件/最近同步；操作：详情/找宠物/远程指令/解绑（二次确认）</t>
+  </si>
+  <si>
+    <t>绑定设备页</t>
+  </si>
+  <si>
+    <t>三步绑定流程</t>
+  </si>
+  <si>
+    <t>①蓝牙扫描（模拟 1.5s，RSSI 信号条 + dBm，支持手动输入 SN）→ ②选择宠物（已绑定宠物不可选）→ ③确认绑定</t>
+  </si>
+  <si>
+    <t>设备详情页</t>
+  </si>
+  <si>
+    <t>设备详情</t>
+  </si>
+  <si>
+    <t>名称/状态/SN/型号；信号强度（0-4 格 + dBm + 刷新）；电量进度条；绑定宠物卡（点击进档案）；IMEI/固件/激活时间/最近同步/电子围栏状态；操作：找宠物/远程指令/解绑</t>
+  </si>
+  <si>
+    <t>数据同步页</t>
+  </si>
+  <si>
+    <t>设备体征上报</t>
+  </si>
+  <si>
+    <t>多设备 Tab；设备状态卡 + 立即同步；最新体征 2×2（体温/心率/血氧/呼吸）；自动上报开关（每 15 秒）；上报记录列表（时间/来源/状态/体征值）</t>
+  </si>
+  <si>
+    <t>宠物档案</t>
+  </si>
+  <si>
+    <t>宠物列表页</t>
+  </si>
+  <si>
+    <t>列表与左滑操作</t>
+  </si>
+  <si>
+    <t>宠物卡片（头像/名/性别/品种·年龄/体重/设备状态或未绑定）；van-swipe-cell 左滑编辑/删除（二次确认）；底部添加宠物</t>
+  </si>
+  <si>
+    <t>添加宠物页</t>
+  </si>
+  <si>
+    <t>档案表单</t>
+  </si>
+  <si>
+    <t>头像上传（预设头像网格）；昵称/物种（犬/猫）/品种选择器（犬 8 种、猫 8 种）/性别/出生日期/体重/绝育开关；护理信息（疫苗/驱虫/性格标签 ≤10）</t>
+  </si>
+  <si>
+    <t>宠物档案页</t>
+  </si>
+  <si>
+    <t>编辑档案</t>
+  </si>
+  <si>
+    <t>头像/昵称/体重/性别/绝育/是否怀孕/是否哺乳开关；只读芯片号与建档时间；护理信息维护（疫苗/驱虫记录增删、性格标签）</t>
+  </si>
+  <si>
+    <t>推送健康数据给医生</t>
+  </si>
+  <si>
+    <t>未推送时「推送医生」弹窗：医生单选列表（头像/姓名·医院/职称/专科）+ 备注 textarea(≤100)；已推送展示医生 + 推送时间 + 修改入口</t>
+  </si>
+  <si>
+    <t>健康报告</t>
+  </si>
+  <si>
+    <t>报告列表页</t>
+  </si>
+  <si>
+    <t>报告列表</t>
+  </si>
+  <si>
+    <t>宠物 Tab 切换；报告卡片：周期/摘要单行省略/健康评分（&lt;85 橙色警示）/异常项标签（N 项异常或正常）/审核状态（待医生审核/已确认/已驳回/AI报告）</t>
+  </si>
+  <si>
+    <t>报告详情页</t>
+  </si>
+  <si>
+    <t>报告详情</t>
+  </si>
+  <si>
+    <t>评分环（conic-gradient）；周期/摘要/标签（异常数、综合评级 A/B/C/D、来源 AI/离线、审核状态）；AI 结论；异常项（数值分级着色 + 建议）；指标概览 2×2；5 张指标趋势图；医生审阅意见；重新生成报告（二次确认）</t>
+  </si>
+  <si>
+    <t>我的/设置</t>
+  </si>
+  <si>
+    <t>我的页</t>
+  </si>
+  <si>
+    <t>个人信息</t>
+  </si>
+  <si>
+    <t>顶部铃铛（未读角标，&gt;99 显示 99+，点击全部已读）+ 设置六边形入口；头像/昵称/订阅套餐标签/个性签名；静态社交统计（粉丝/关注/获赞）；四宫格入口（宠物/设备/问诊/报告）；列表菜单（我的发布/百科占位、订阅服务）；切换角色；版本页脚</t>
+  </si>
+  <si>
+    <t>社交统计为静态</t>
+  </si>
+  <si>
+    <t>设置页</t>
+  </si>
+  <si>
+    <t>设置中心</t>
+  </si>
+  <si>
+    <t>账号信息 / 修改密码（验证码登录用户不展示）/ 系统语言开关（中英）/ 意见反馈 / 关于我们 / 版本信息 / 服务与隐私 / 清除缓存（测量大小+二次确认）/ 注销账号（danger）/ 退出登录（二次确认）</t>
+  </si>
+  <si>
+    <t>账号信息页</t>
+  </si>
+  <si>
+    <t>编辑账号资料</t>
+  </si>
+  <si>
+    <t>头像（预设网格选择）/ 昵称(≤20) / 只读注册账号与用户 ID / 性别 radio / 生日（1940-今天）/ 地区选择 / 个人简介(≤100)；保存同步登录态</t>
+  </si>
+  <si>
+    <t>修改密码页</t>
+  </si>
+  <si>
+    <t>修改登录密码</t>
+  </si>
+  <si>
+    <t>原密码 + 新密码 + 确认新密码；规则：6-20 位须含字母+数字；成功后自动退出并回登录页</t>
+  </si>
+  <si>
+    <t>意见反馈页</t>
+  </si>
+  <si>
+    <t>FAQ 与反馈</t>
+  </si>
+  <si>
+    <t>Tab1 常见问题（手风琴双语）；Tab2 意见反馈（主题 ≤30 / 描述 ≤500 / 图片 ≤6 张 ≤5MB）；Tab3 历史记录（状态标签/内容/时间）</t>
+  </si>
+  <si>
+    <t>关于我们/版本/服务</t>
+  </si>
+  <si>
+    <t>品牌与协议</t>
+  </si>
+  <si>
+    <t>关于我们：品牌介绍 + 版权；版本信息：检查更新/更新日志/模拟下载进度；服务与隐私：协议列表 + 章节自动识别正文</t>
+  </si>
+  <si>
+    <t>注销账号页</t>
+  </si>
+  <si>
+    <t>注销账号</t>
+  </si>
+  <si>
+    <t>注销须知（红色警示卡，法律保留数据 180 天后删除）；后果列表 4 条；勾选协议（链接协议详情）后注销；二次确认 → 退出登录</t>
+  </si>
+  <si>
+    <t>订阅服务页</t>
+  </si>
+  <si>
+    <t>套餐与订单</t>
+  </si>
+  <si>
+    <t>套餐卡片（基础/专业/尊享：时长/价格/权益列表/立即订阅）；二次确认下单；最近订单（套餐名/订单号/时间/金额）</t>
+  </si>
+  <si>
+    <t>AI 助手页</t>
+  </si>
+  <si>
+    <t>AI 智能对话</t>
+  </si>
+  <si>
+    <t>语音播报开关；宠物 Tab 切换；聊天气泡；示例问法 chips；语音输入（Web Speech API）；意图识别（找宠物/亮灯/定位/健康/报告）→ 触发远程指令或路由跳转</t>
+  </si>
+  <si>
+    <t>占位功能</t>
+  </si>
+  <si>
+    <t>各占位路由</t>
+  </si>
+  <si>
+    <t>运动趋势/食谱/翻译/自查/相册/账本/待办/我的发布/百科</t>
+  </si>
+  <si>
+    <t>以上功能使用 FeaturePlaceholder 通用占位页（「功能开发中」空态），图标与标题由路由 meta 控制</t>
+  </si>
+  <si>
+    <t>9 处占位入口</t>
+  </si>
+  <si>
+    <t>医生登录</t>
+  </si>
+  <si>
+    <t>品牌区 + 账号/密码表单（明文切换，回车提交）；演示账号一键登录（doctor/123456）；仅密码登录模式，无协议勾选；角色不匹配提示「该账号不属于当前入口」</t>
+  </si>
+  <si>
     <t>已实现</t>
-  </si>
-  <si>
-    <t>支持账号/手机号/邮箱登录</t>
-  </si>
-  <si>
-    <t>验证码登录</t>
-  </si>
-  <si>
-    <t>联系类型 Tab（手机号 / 邮箱）+ 国际区号选择（action-sheet）；6 位验证码 + 获取验证码倒计时</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>记住我</t>
-  </si>
-  <si>
-    <t>勾选后登录态写入 localStorage（跨会话），否则仅 sessionStorage</t>
-  </si>
-  <si>
-    <t>sp_token / sp_role</t>
-  </si>
-  <si>
-    <t>协议勾选</t>
-  </si>
-  <si>
-    <t>服务协议 + 隐私政策链接（可查看详情），勾选后方可提交</t>
-  </si>
-  <si>
-    <t>Agreement.vue</t>
-  </si>
-  <si>
-    <t>第三方登录</t>
-  </si>
-  <si>
-    <t>Google / Apple 登录按钮，点击提示「敬请期待」</t>
-  </si>
-  <si>
-    <t>占位</t>
-  </si>
-  <si>
-    <t>演示账号一键登录</t>
-  </si>
-  <si>
-    <t>本端演示账号卡片（user/123456）一键填充</t>
-  </si>
-  <si>
-    <t>注册页</t>
-  </si>
-  <si>
-    <t>手机号/邮箱注册</t>
-  </si>
-  <si>
-    <t>联系类型 Tab + 区号选择；验证码获取（60s 倒计时）；密码 + 确认密码（明文切换）；协议勾选；注册成功回登录页预填账号</t>
-  </si>
-  <si>
-    <t>角色强绑定 user</t>
-  </si>
-  <si>
-    <t>找回密码页</t>
-  </si>
-  <si>
-    <t>重置密码</t>
-  </si>
-  <si>
-    <t>手机号/邮箱 + 验证码（scene=reset）+ 新密码 + 确认新密码；成功回登录页预填账号</t>
-  </si>
-  <si>
-    <t>首页</t>
-  </si>
-  <si>
-    <t>宠物切换条</t>
-  </si>
-  <si>
-    <t>宠物切换与添加</t>
-  </si>
-  <si>
-    <t>顶部横向头像栏展示名下宠物（最多 3 只），点击切换当前宠物；末尾「+」跳转添加宠物；无宠物展示空态引导</t>
-  </si>
-  <si>
-    <t>宠物健康卡片</t>
-  </si>
-  <si>
-    <t>健康概览 Hero 卡片</t>
-  </si>
-  <si>
-    <t>物种图标 + 宠物名、性别、年龄、品种、体重(kg)、洗澡/驱虫/疫苗计数；点击进入宠物档案</t>
-  </si>
-  <si>
-    <t>功能模块宫格</t>
-  </si>
-  <si>
-    <t>宠物相册</t>
-  </si>
-  <si>
-    <t>2×2 宫格入口，跳转相册页</t>
-  </si>
-  <si>
-    <t>FeaturePlaceholder</t>
-  </si>
-  <si>
-    <t>待办事项</t>
-  </si>
-  <si>
-    <t>宫格入口，跳转待办页</t>
-  </si>
-  <si>
-    <t>养宠账本</t>
-  </si>
-  <si>
-    <t>宫格入口，跳转账本页</t>
-  </si>
-  <si>
-    <t>底部快捷操作栏</t>
-  </si>
-  <si>
-    <t>快捷入口（5 个）</t>
-  </si>
-  <si>
-    <t>在线问诊 / AI助手 / 宠物食谱 / 宠物翻译 / 健康自查 圆形按钮；问诊与 AI 助手已实现，其余占位</t>
-  </si>
-  <si>
-    <t>部分占位</t>
-  </si>
-  <si>
-    <t>汉堡菜单</t>
-  </si>
-  <si>
-    <t>宠物管理入口</t>
-  </si>
-  <si>
-    <t>右上角汉堡菜单支持语言切换与宠物管理入口</t>
-  </si>
-  <si>
-    <t>守护/健康监测</t>
-  </si>
-  <si>
-    <t>守护页 Health.vue</t>
-  </si>
-  <si>
-    <t>地图与轨迹展示</t>
-  </si>
-  <si>
-    <t>全屏高德地图展示宠物当前轨迹连线 + 电子围栏范围；宠物 Tab 切换监测对象</t>
-  </si>
-  <si>
-    <t>Amap 组件</t>
-  </si>
-  <si>
-    <t>守护页</t>
-  </si>
-  <si>
-    <t>宠物头部信息</t>
-  </si>
-  <si>
-    <t>宠物头像 / 名称 / 项圈设备名 / 设备状态标签（在线/离线/低电量/未绑定）/ 电量百分比 / 位置地址 + 围栏内外标注</t>
-  </si>
-  <si>
-    <t>健康指标（5 项）</t>
-  </si>
-  <si>
-    <t>体温 / 心率 / 血氧 / 呼吸 / 卡路里 实时卡片，点击进入体征详情页</t>
-  </si>
-  <si>
-    <t>VitalDetail</t>
-  </si>
-  <si>
-    <t>运动指标（4 项）</t>
-  </si>
-  <si>
-    <t>步频 / 步幅 / 步态 / 速度 实时卡片，「运动趋势」跳转</t>
-  </si>
-  <si>
-    <t>运动趋势占位</t>
-  </si>
-  <si>
-    <t>电子围栏入口</t>
-  </si>
-  <si>
-    <t>快捷工具入口，带固定围栏数量角标，跳转围栏管理</t>
-  </si>
-  <si>
-    <t>语音对讲</t>
-  </si>
-  <si>
-    <t>按住说话（MediaRecorder 录音）、上滑取消、模拟对方回复（speechSynthesis 语音播报）</t>
-  </si>
-  <si>
-    <t>远程指令</t>
-  </si>
-  <si>
-    <t>指令面板：响铃(find)/警示灯(light)/请求定位(refresh)；设备离线时禁用并提示</t>
-  </si>
-  <si>
-    <t>commandDeviceApi</t>
-  </si>
-  <si>
-    <t>体征详情页</t>
-  </si>
-  <si>
-    <t>指标切换与周期选择</t>
-  </si>
-  <si>
-    <t>体温/血氧/心率/呼吸/卡路里 5 指标 Tab；周期：单日/本周/本月/本季度（1/7/30/90 天）；单日仅当天有数据</t>
-  </si>
-  <si>
-    <t>趋势图与健康分析</t>
-  </si>
-  <si>
-    <t>趋势图按健康等级着色（正常绿/预警橙/危险红）；周期四指标分析报告（均值/最值/健康等级/建议/整体结论），分级阈值按犬/猫区分</t>
-  </si>
-  <si>
-    <t>VitalDetailChart</t>
-  </si>
-  <si>
-    <t>位置与轨迹</t>
-  </si>
-  <si>
-    <t>轨迹查看页</t>
-  </si>
-  <si>
-    <t>时间范围选择</t>
-  </si>
-  <si>
-    <t>今天 / 近 3 天 / 近 7 天 / 自定义（van-calendar，最小 30 天前）</t>
-  </si>
-  <si>
-    <t>轨迹展示</t>
-  </si>
-  <si>
-    <t>高德地图轨迹点连线，抽稀最多 150 点保证性能</t>
-  </si>
-  <si>
-    <t>轨迹汇总</t>
-  </si>
-  <si>
-    <t>宠物头像 / 名称 / 时间范围文案 / 轨迹点数 / 总里程（haversine 距离累加）；无轨迹空态</t>
-  </si>
-  <si>
-    <t>电子围栏</t>
-  </si>
-  <si>
-    <t>围栏管理页</t>
-  </si>
-  <si>
-    <t>动态围栏（跟随手机）</t>
-  </si>
-  <si>
-    <t>启用开关；距手机距离 + 围栏内/外/已关闭状态；半径滑杆（100-3000m，步长 50）+ 快捷预设（200/500/800/1500m）</t>
-  </si>
-  <si>
-    <t>仅一条</t>
-  </si>
-  <si>
-    <t>固定围栏列表</t>
-  </si>
-  <si>
-    <t>围栏名称 / 启用开关 / 半径 / 物理地址 / 编辑 / 删除（二次确认）</t>
-  </si>
-  <si>
-    <t>地址前端生成</t>
-  </si>
-  <si>
-    <t>新增固定围栏</t>
-  </si>
-  <si>
-    <t>地图选点（拖动/点击选中心点）→ 表单：名称(maxlength 20)/坐标展示/重新选点/半径滑杆/保存</t>
-  </si>
-  <si>
-    <t>增删改真实生效</t>
-  </si>
-  <si>
-    <t>宠圈社区</t>
-  </si>
-  <si>
-    <t>社区首页</t>
-  </si>
-  <si>
-    <t>信息流与搜索</t>
-  </si>
-  <si>
-    <t>按 caption / 宠物名 / 作者名 关键字搜索；宠物圈 / 关注萌宠 双 Tab；van-list 无限滚动分页</t>
-  </si>
-  <si>
-    <t>帖子卡片</t>
-  </si>
-  <si>
-    <t>作者头像/名/会员等级标签/相对时间；关注/已关注切换（取关实时移除）；文案/图片（最多 3 张 +N 角标）；浏览/点赞（橙色高亮）/评论数</t>
-  </si>
-  <si>
-    <t>帖子详情页</t>
-  </si>
-  <si>
-    <t>详情与评论</t>
-  </si>
-  <si>
-    <t>全部图片 2 列网格；关注/点赞切换；评论列表 + 底部评论栏（发送，回车提交，评论数 +1）</t>
-  </si>
-  <si>
-    <t>在线问诊</t>
-  </si>
-  <si>
-    <t>医生列表页</t>
-  </si>
-  <si>
-    <t>搜索与科室筛选</t>
-  </si>
-  <si>
-    <t>按姓名/医院搜索；科室分类：口腔 / 眼科 / 内科 切换</t>
-  </si>
-  <si>
-    <t>医生卡片与发起</t>
-  </si>
-  <si>
-    <t>头像/姓名/职称/医院·科室/咨询价（¥）/「马上咨询」→ 选择宠物 → 跳发起问诊；无宠物提示并引导绑定</t>
-  </si>
-  <si>
-    <t>发起问诊页</t>
-  </si>
-  <si>
-    <t>咨询内容与图片</t>
-  </si>
-  <si>
-    <t>医生信息卡 + 宠物信息卡；病情描述（必填 maxlength 500 字数统计）；图片上传最多 6 张单张 ≤5MB</t>
-  </si>
-  <si>
-    <t>健康/运动快照</t>
-  </si>
-  <si>
-    <t>只读推送近期待检体征快照（体温/心率/血氧/呼吸/卡路里/活动度/睡眠）+ 运动快照（步频/步幅/步态/速度）</t>
-  </si>
-  <si>
-    <t>问诊记录页</t>
-  </si>
-  <si>
-    <t>记录列表</t>
-  </si>
-  <si>
-    <t>宠物头像/名、医生姓名·发起时间、状态标签（进行中/已结束）、病情描述 2 行截断、最新回复预览或等待回复；右下角悬浮问诊按钮</t>
-  </si>
-  <si>
-    <t>问诊详情页</t>
-  </si>
-  <si>
-    <t>详情与医生回复</t>
-  </si>
-  <si>
-    <t>状态/发起时间；医生卡、宠物卡、病情描述、图片大图预览；健康/运动快照；医生回复卡片 + 推荐用药（名称+用法用量）/无用药建议；等待中闪烁提示</t>
-  </si>
-  <si>
-    <t>设备管理</t>
-  </si>
-  <si>
-    <t>设备列表页</t>
-  </si>
-  <si>
-    <t>设备卡片与操作</t>
-  </si>
-  <si>
-    <t>设备总数 + 绑定按钮；卡片含名称/状态标签/SN/低电量红标/电量进度条/固件/最近同步；操作：详情/找宠物/远程指令/解绑（二次确认）</t>
-  </si>
-  <si>
-    <t>绑定设备页</t>
-  </si>
-  <si>
-    <t>三步绑定流程</t>
-  </si>
-  <si>
-    <t>①蓝牙扫描（模拟 1.5s，RSSI 信号条 + dBm，支持手动输入 SN）→ ②选择宠物（已绑定宠物不可选）→ ③确认绑定</t>
-  </si>
-  <si>
-    <t>设备详情页</t>
-  </si>
-  <si>
-    <t>设备详情</t>
-  </si>
-  <si>
-    <t>名称/状态/SN/型号；信号强度（0-4 格 + dBm + 刷新）；电量进度条；绑定宠物卡（点击进档案）；IMEI/固件/激活时间/最近同步/电子围栏状态；操作：找宠物/远程指令/解绑</t>
-  </si>
-  <si>
-    <t>数据同步页</t>
-  </si>
-  <si>
-    <t>设备体征上报</t>
-  </si>
-  <si>
-    <t>多设备 Tab；设备状态卡 + 立即同步；最新体征 2×2（体温/心率/血氧/呼吸）；自动上报开关（每 15 秒）；上报记录列表（时间/来源/状态/体征值）</t>
-  </si>
-  <si>
-    <t>宠物档案</t>
-  </si>
-  <si>
-    <t>宠物列表页</t>
-  </si>
-  <si>
-    <t>列表与左滑操作</t>
-  </si>
-  <si>
-    <t>宠物卡片（头像/名/性别/品种·年龄/体重/设备状态或未绑定）；van-swipe-cell 左滑编辑/删除（二次确认）；底部添加宠物</t>
-  </si>
-  <si>
-    <t>添加宠物页</t>
-  </si>
-  <si>
-    <t>档案表单</t>
-  </si>
-  <si>
-    <t>头像上传（预设头像网格）；昵称/物种（犬/猫）/品种选择器（犬 8 种、猫 8 种）/性别/出生日期/体重/绝育开关；护理信息（疫苗/驱虫/性格标签 ≤10）</t>
-  </si>
-  <si>
-    <t>宠物档案页</t>
-  </si>
-  <si>
-    <t>编辑档案</t>
-  </si>
-  <si>
-    <t>头像/昵称/体重/性别/绝育/是否怀孕/是否哺乳开关；只读芯片号与建档时间；护理信息维护（疫苗/驱虫记录增删、性格标签）</t>
-  </si>
-  <si>
-    <t>推送健康数据给医生</t>
-  </si>
-  <si>
-    <t>未推送时「推送医生」弹窗：医生单选列表（头像/姓名·医院/职称/专科）+ 备注 textarea(≤100)；已推送展示医生 + 推送时间 + 修改入口</t>
-  </si>
-  <si>
-    <t>健康报告</t>
-  </si>
-  <si>
-    <t>报告列表页</t>
-  </si>
-  <si>
-    <t>报告列表</t>
-  </si>
-  <si>
-    <t>宠物 Tab 切换；报告卡片：周期/摘要单行省略/健康评分（&lt;85 橙色警示）/异常项标签（N 项异常或正常）/审核状态（待医生审核/已确认/已驳回/AI报告）</t>
-  </si>
-  <si>
-    <t>报告详情页</t>
-  </si>
-  <si>
-    <t>报告详情</t>
-  </si>
-  <si>
-    <t>评分环（conic-gradient）；周期/摘要/标签（异常数、综合评级 A/B/C/D、来源 AI/离线、审核状态）；AI 结论；异常项（数值分级着色 + 建议）；指标概览 2×2；5 张指标趋势图；医生审阅意见；重新生成报告（二次确认）</t>
-  </si>
-  <si>
-    <t>我的/设置</t>
-  </si>
-  <si>
-    <t>我的页</t>
-  </si>
-  <si>
-    <t>个人信息</t>
-  </si>
-  <si>
-    <t>顶部铃铛（未读角标，&gt;99 显示 99+，点击全部已读）+ 设置六边形入口；头像/昵称/订阅套餐标签/个性签名；静态社交统计（粉丝/关注/获赞）；四宫格入口（宠物/设备/问诊/报告）；列表菜单（我的发布/百科占位、订阅服务）；切换角色；版本页脚</t>
-  </si>
-  <si>
-    <t>社交统计为静态</t>
-  </si>
-  <si>
-    <t>设置页</t>
-  </si>
-  <si>
-    <t>设置中心</t>
-  </si>
-  <si>
-    <t>账号信息 / 修改密码（验证码登录用户不展示）/ 系统语言开关（中英）/ 意见反馈 / 关于我们 / 版本信息 / 服务与隐私 / 清除缓存（测量大小+二次确认）/ 注销账号（danger）/ 退出登录（二次确认）</t>
-  </si>
-  <si>
-    <t>账号信息页</t>
-  </si>
-  <si>
-    <t>编辑账号资料</t>
-  </si>
-  <si>
-    <t>头像（预设网格选择）/ 昵称(≤20) / 只读注册账号与用户 ID / 性别 radio / 生日（1940-今天）/ 地区选择 / 个人简介(≤100)；保存同步登录态</t>
-  </si>
-  <si>
-    <t>修改密码页</t>
-  </si>
-  <si>
-    <t>修改登录密码</t>
-  </si>
-  <si>
-    <t>原密码 + 新密码 + 确认新密码；规则：6-20 位须含字母+数字；成功后自动退出并回登录页</t>
-  </si>
-  <si>
-    <t>意见反馈页</t>
-  </si>
-  <si>
-    <t>FAQ 与反馈</t>
-  </si>
-  <si>
-    <t>Tab1 常见问题（手风琴双语）；Tab2 意见反馈（主题 ≤30 / 描述 ≤500 / 图片 ≤6 张 ≤5MB）；Tab3 历史记录（状态标签/内容/时间）</t>
-  </si>
-  <si>
-    <t>关于我们/版本/服务</t>
-  </si>
-  <si>
-    <t>品牌与协议</t>
-  </si>
-  <si>
-    <t>关于我们：品牌介绍 + 版权；版本信息：检查更新/更新日志/模拟下载进度；服务与隐私：协议列表 + 章节自动识别正文</t>
-  </si>
-  <si>
-    <t>注销账号页</t>
-  </si>
-  <si>
-    <t>注销账号</t>
-  </si>
-  <si>
-    <t>注销须知（红色警示卡，法律保留数据 180 天后删除）；后果列表 4 条；勾选协议（链接协议详情）后注销；二次确认 → 退出登录</t>
-  </si>
-  <si>
-    <t>订阅服务页</t>
-  </si>
-  <si>
-    <t>套餐与订单</t>
-  </si>
-  <si>
-    <t>套餐卡片（基础/专业/尊享：时长/价格/权益列表/立即订阅）；二次确认下单；最近订单（套餐名/订单号/时间/金额）</t>
-  </si>
-  <si>
-    <t>AI 助手页</t>
-  </si>
-  <si>
-    <t>AI 智能对话</t>
-  </si>
-  <si>
-    <t>语音播报开关；宠物 Tab 切换；聊天气泡；示例问法 chips；语音输入（Web Speech API）；意图识别（找宠物/亮灯/定位/健康/报告）→ 触发远程指令或路由跳转</t>
-  </si>
-  <si>
-    <t>占位功能</t>
-  </si>
-  <si>
-    <t>各占位路由</t>
-  </si>
-  <si>
-    <t>运动趋势/食谱/翻译/自查/相册/账本/待办/我的发布/百科</t>
-  </si>
-  <si>
-    <t>以上功能使用 FeaturePlaceholder 通用占位页（「功能开发中」空态），图标与标题由路由 meta 控制</t>
-  </si>
-  <si>
-    <t>9 处占位入口</t>
-  </si>
-  <si>
-    <t>医生登录</t>
-  </si>
-  <si>
-    <t>品牌区 + 账号/密码表单（明文切换，回车提交）；演示账号一键登录（doctor/123456）；仅密码登录模式，无协议勾选；角色不匹配提示「该账号不属于当前入口」</t>
   </si>
   <si>
     <t>useLoginForm 复用</t>
@@ -2565,7 +2562,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I61"/>
+  <dimension ref="A1:I64"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
@@ -2734,9 +2731,7 @@
       <c r="E7" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="F7" s="8" t="s">
-        <v>68</v>
-      </c>
+      <c r="F7" s="8"/>
       <c r="G7" s="2" t="s">
         <v>59</v>
       </c>
@@ -2751,14 +2746,12 @@
         <v>52</v>
       </c>
       <c r="D8" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="E8" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="E8" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>55</v>
-      </c>
+      <c r="F8" s="2"/>
       <c r="G8" s="2" t="s">
         <v>59</v>
       </c>
@@ -2770,19 +2763,17 @@
       </c>
       <c r="B9" s="5"/>
       <c r="C9" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="D9" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="D9" s="4" t="s">
+      <c r="E9" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="E9" s="4" t="s">
+      <c r="F9" s="2"/>
+      <c r="G9" s="2" t="s">
         <v>73</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>74</v>
       </c>
       <c r="H9" s="4"/>
     </row>
@@ -2792,17 +2783,15 @@
       </c>
       <c r="B10" s="6"/>
       <c r="C10" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="D10" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="D10" s="4" t="s">
+      <c r="E10" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="E10" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>55</v>
-      </c>
+      <c r="F10" s="2"/>
       <c r="G10" s="2" t="s">
         <v>59</v>
       </c>
@@ -2813,16 +2802,16 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="C11" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="C11" s="4" t="s">
+      <c r="D11" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="D11" s="4" t="s">
+      <c r="E11" s="4" t="s">
         <v>80</v>
-      </c>
-      <c r="E11" s="4" t="s">
-        <v>81</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>55</v>
@@ -2838,13 +2827,13 @@
       </c>
       <c r="B12" s="5"/>
       <c r="C12" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="D12" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="D12" s="4" t="s">
+      <c r="E12" s="4" t="s">
         <v>83</v>
-      </c>
-      <c r="E12" s="4" t="s">
-        <v>84</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>55</v>
@@ -2860,19 +2849,17 @@
       </c>
       <c r="B13" s="5"/>
       <c r="C13" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="D13" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="D13" s="4" t="s">
+      <c r="E13" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="E13" s="4" t="s">
+      <c r="F13" s="8"/>
+      <c r="G13" s="2" t="s">
         <v>87</v>
-      </c>
-      <c r="F13" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="G13" s="2" t="s">
-        <v>88</v>
       </c>
       <c r="H13" s="4"/>
     </row>
@@ -2882,191 +2869,151 @@
       </c>
       <c r="B14" s="5"/>
       <c r="C14" s="4" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D14" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="E14" s="4" t="s">
         <v>89</v>
       </c>
-      <c r="E14" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="F14" s="8" t="s">
-        <v>68</v>
-      </c>
+      <c r="F14" s="8"/>
       <c r="G14" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="H14" s="4"/>
     </row>
     <row r="15" spans="1:9">
       <c r="A15" s="2">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B15" s="5"/>
       <c r="C15" s="4" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="D15" s="4" t="s">
         <v>91</v>
       </c>
-      <c r="E15" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="F15" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="G15" s="2" t="s">
-        <v>88</v>
-      </c>
+      <c r="E15" s="4"/>
+      <c r="F15" s="2"/>
+      <c r="G15" s="2"/>
       <c r="H15" s="4"/>
     </row>
-    <row r="16" ht="31" spans="1:9">
-      <c r="A16" s="2">
-        <v>15</v>
-      </c>
+    <row r="16" spans="1:9">
+      <c r="A16" s="2"/>
       <c r="B16" s="5"/>
       <c r="C16" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="E16" s="4"/>
+      <c r="F16" s="2"/>
+      <c r="G16" s="2"/>
+      <c r="H16" s="4"/>
+    </row>
+    <row r="17" spans="1:8">
+      <c r="A17" s="2"/>
+      <c r="B17" s="5"/>
+      <c r="C17" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="D17" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="D16" s="4" t="s">
+      <c r="E17" s="4"/>
+      <c r="F17" s="2"/>
+      <c r="G17" s="2"/>
+      <c r="H17" s="4"/>
+    </row>
+    <row r="18" spans="1:8">
+      <c r="A18" s="2"/>
+      <c r="B18" s="5"/>
+      <c r="C18" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="D18" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="E16" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="G16" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="H16" s="4"/>
-    </row>
-    <row r="17" spans="1:8">
-      <c r="A17" s="2">
-        <v>16</v>
-      </c>
-      <c r="B17" s="6"/>
-      <c r="C17" s="4" t="s">
-        <v>97</v>
-      </c>
-      <c r="D17" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="E17" s="4" t="s">
-        <v>99</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="G17" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="H17" s="4"/>
-    </row>
-    <row r="18" spans="1:8">
-      <c r="A18" s="2">
-        <v>17</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="C18" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="D18" s="4" t="s">
-        <v>102</v>
-      </c>
-      <c r="E18" s="4" t="s">
-        <v>103</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="G18" s="2" t="s">
-        <v>104</v>
-      </c>
+      <c r="E18" s="4"/>
+      <c r="F18" s="2"/>
+      <c r="G18" s="2"/>
       <c r="H18" s="4"/>
     </row>
-    <row r="19" ht="31" spans="1:8">
-      <c r="A19" s="2">
-        <v>18</v>
-      </c>
+    <row r="19" spans="1:8">
+      <c r="A19" s="2"/>
       <c r="B19" s="5"/>
       <c r="C19" s="4" t="s">
-        <v>105</v>
+        <v>90</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>106</v>
-      </c>
-      <c r="E19" s="4" t="s">
-        <v>107</v>
-      </c>
-      <c r="F19" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="G19" s="2" t="s">
-        <v>59</v>
-      </c>
+        <v>95</v>
+      </c>
+      <c r="E19" s="4"/>
+      <c r="F19" s="2"/>
+      <c r="G19" s="2"/>
       <c r="H19" s="4"/>
     </row>
     <row r="20" spans="1:8">
       <c r="A20" s="2">
-        <v>19</v>
-      </c>
-      <c r="B20" s="5"/>
+        <v>16</v>
+      </c>
+      <c r="B20" s="6"/>
       <c r="C20" s="4" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>108</v>
+        <v>97</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>109</v>
+        <v>98</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>55</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>110</v>
+        <v>59</v>
       </c>
       <c r="H20" s="4"/>
     </row>
     <row r="21" spans="1:8">
       <c r="A21" s="2">
-        <v>20</v>
-      </c>
-      <c r="B21" s="5"/>
+        <v>17</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>99</v>
+      </c>
       <c r="C21" s="4" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>111</v>
+        <v>101</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>112</v>
+        <v>102</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>55</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="H21" s="4"/>
     </row>
-    <row r="22" spans="1:8">
+    <row r="22" ht="31" spans="1:8">
       <c r="A22" s="2">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B22" s="5"/>
       <c r="C22" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="D22" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="D22" s="4" t="s">
-        <v>114</v>
-      </c>
       <c r="E22" s="4" t="s">
-        <v>115</v>
+        <v>106</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>55</v>
@@ -3076,63 +3023,63 @@
       </c>
       <c r="H22" s="4"/>
     </row>
-    <row r="23" ht="31" spans="1:8">
+    <row r="23" spans="1:8">
       <c r="A23" s="2">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="B23" s="5"/>
       <c r="C23" s="4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>116</v>
+        <v>107</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>55</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>59</v>
+        <v>109</v>
       </c>
       <c r="H23" s="4"/>
     </row>
     <row r="24" spans="1:8">
       <c r="A24" s="2">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="B24" s="5"/>
       <c r="C24" s="4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>55</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>120</v>
+        <v>112</v>
       </c>
       <c r="H24" s="4"/>
     </row>
-    <row r="25" ht="31" spans="1:8">
+    <row r="25" spans="1:8">
       <c r="A25" s="2">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="B25" s="5"/>
       <c r="C25" s="4" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>122</v>
+        <v>113</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>123</v>
+        <v>114</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>55</v>
@@ -3144,63 +3091,61 @@
     </row>
     <row r="26" ht="31" spans="1:8">
       <c r="A26" s="2">
-        <v>25</v>
-      </c>
-      <c r="B26" s="6"/>
+        <v>22</v>
+      </c>
+      <c r="B26" s="5"/>
       <c r="C26" s="4" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>124</v>
+        <v>115</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>125</v>
+        <v>116</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>55</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>126</v>
+        <v>59</v>
       </c>
       <c r="H26" s="4"/>
     </row>
     <row r="27" spans="1:8">
       <c r="A27" s="2">
-        <v>26</v>
-      </c>
-      <c r="B27" s="3" t="s">
-        <v>127</v>
-      </c>
+        <v>23</v>
+      </c>
+      <c r="B27" s="5"/>
       <c r="C27" s="4" t="s">
-        <v>128</v>
+        <v>104</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>129</v>
+        <v>117</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>130</v>
+        <v>118</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>55</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>59</v>
+        <v>119</v>
       </c>
       <c r="H27" s="4"/>
     </row>
-    <row r="28" spans="1:8">
+    <row r="28" ht="31" spans="1:8">
       <c r="A28" s="2">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="B28" s="5"/>
       <c r="C28" s="4" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>131</v>
+        <v>121</v>
       </c>
       <c r="E28" s="4" t="s">
-        <v>132</v>
+        <v>122</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>55</v>
@@ -3212,181 +3157,167 @@
     </row>
     <row r="29" ht="31" spans="1:8">
       <c r="A29" s="2">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="B29" s="6"/>
       <c r="C29" s="4" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>133</v>
+        <v>123</v>
       </c>
       <c r="E29" s="4" t="s">
-        <v>134</v>
+        <v>124</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>55</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>59</v>
+        <v>125</v>
       </c>
       <c r="H29" s="4"/>
     </row>
-    <row r="30" ht="31" spans="1:8">
+    <row r="30" spans="1:8">
       <c r="A30" s="2">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>135</v>
+        <v>126</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>136</v>
+        <v>127</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>137</v>
+        <v>128</v>
       </c>
       <c r="E30" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="F30" s="2" t="s">
-        <v>55</v>
-      </c>
+        <v>129</v>
+      </c>
+      <c r="F30" s="2"/>
       <c r="G30" s="2" t="s">
-        <v>139</v>
+        <v>59</v>
       </c>
       <c r="H30" s="4"/>
     </row>
     <row r="31" spans="1:8">
       <c r="A31" s="2">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="B31" s="5"/>
       <c r="C31" s="4" t="s">
-        <v>136</v>
+        <v>127</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>141</v>
-      </c>
-      <c r="F31" s="2" t="s">
-        <v>55</v>
-      </c>
+        <v>131</v>
+      </c>
+      <c r="F31" s="2"/>
       <c r="G31" s="2" t="s">
-        <v>142</v>
+        <v>59</v>
       </c>
       <c r="H31" s="4"/>
     </row>
     <row r="32" ht="31" spans="1:8">
       <c r="A32" s="2">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="B32" s="6"/>
       <c r="C32" s="4" t="s">
-        <v>136</v>
+        <v>127</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>143</v>
+        <v>132</v>
       </c>
       <c r="E32" s="4" t="s">
-        <v>144</v>
-      </c>
-      <c r="F32" s="2" t="s">
-        <v>55</v>
-      </c>
+        <v>133</v>
+      </c>
+      <c r="F32" s="2"/>
       <c r="G32" s="2" t="s">
-        <v>145</v>
+        <v>59</v>
       </c>
       <c r="H32" s="4"/>
     </row>
     <row r="33" ht="31" spans="1:8">
       <c r="A33" s="2">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>146</v>
+        <v>134</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>147</v>
+        <v>135</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>148</v>
+        <v>136</v>
       </c>
       <c r="E33" s="4" t="s">
-        <v>149</v>
-      </c>
-      <c r="F33" s="2" t="s">
-        <v>55</v>
-      </c>
+        <v>137</v>
+      </c>
+      <c r="F33" s="2"/>
       <c r="G33" s="2" t="s">
-        <v>59</v>
+        <v>138</v>
       </c>
       <c r="H33" s="4"/>
     </row>
-    <row r="34" ht="31" spans="1:8">
+    <row r="34" spans="1:8">
       <c r="A34" s="2">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="B34" s="5"/>
       <c r="C34" s="4" t="s">
-        <v>147</v>
+        <v>135</v>
       </c>
       <c r="D34" s="4" t="s">
-        <v>150</v>
+        <v>139</v>
       </c>
       <c r="E34" s="4" t="s">
-        <v>151</v>
-      </c>
-      <c r="F34" s="2" t="s">
-        <v>55</v>
-      </c>
+        <v>140</v>
+      </c>
+      <c r="F34" s="2"/>
       <c r="G34" s="2" t="s">
-        <v>59</v>
+        <v>141</v>
       </c>
       <c r="H34" s="4"/>
     </row>
     <row r="35" ht="31" spans="1:8">
       <c r="A35" s="2">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="B35" s="6"/>
       <c r="C35" s="4" t="s">
-        <v>152</v>
+        <v>135</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>153</v>
+        <v>142</v>
       </c>
       <c r="E35" s="4" t="s">
-        <v>154</v>
-      </c>
-      <c r="F35" s="2" t="s">
-        <v>55</v>
-      </c>
+        <v>143</v>
+      </c>
+      <c r="F35" s="2"/>
       <c r="G35" s="2" t="s">
-        <v>59</v>
+        <v>144</v>
       </c>
       <c r="H35" s="4"/>
     </row>
-    <row r="36" spans="1:8">
+    <row r="36" ht="31" spans="1:8">
       <c r="A36" s="2">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>155</v>
+        <v>145</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
       <c r="D36" s="4" t="s">
-        <v>157</v>
+        <v>147</v>
       </c>
       <c r="E36" s="4" t="s">
-        <v>158</v>
-      </c>
-      <c r="F36" s="2" t="s">
-        <v>55</v>
-      </c>
+        <v>148</v>
+      </c>
+      <c r="F36" s="2"/>
       <c r="G36" s="2" t="s">
         <v>59</v>
       </c>
@@ -3394,21 +3325,19 @@
     </row>
     <row r="37" ht="31" spans="1:8">
       <c r="A37" s="2">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="B37" s="5"/>
       <c r="C37" s="4" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
       <c r="D37" s="4" t="s">
-        <v>159</v>
+        <v>149</v>
       </c>
       <c r="E37" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="F37" s="2" t="s">
-        <v>55</v>
-      </c>
+        <v>150</v>
+      </c>
+      <c r="F37" s="2"/>
       <c r="G37" s="2" t="s">
         <v>59</v>
       </c>
@@ -3416,43 +3345,41 @@
     </row>
     <row r="38" ht="31" spans="1:8">
       <c r="A38" s="2">
-        <v>37</v>
-      </c>
-      <c r="B38" s="5"/>
+        <v>34</v>
+      </c>
+      <c r="B38" s="6"/>
       <c r="C38" s="4" t="s">
-        <v>161</v>
+        <v>151</v>
       </c>
       <c r="D38" s="4" t="s">
-        <v>162</v>
+        <v>152</v>
       </c>
       <c r="E38" s="4" t="s">
-        <v>163</v>
-      </c>
-      <c r="F38" s="2" t="s">
-        <v>55</v>
-      </c>
+        <v>153</v>
+      </c>
+      <c r="F38" s="2"/>
       <c r="G38" s="2" t="s">
         <v>59</v>
       </c>
       <c r="H38" s="4"/>
     </row>
-    <row r="39" ht="31" spans="1:8">
+    <row r="39" spans="1:8">
       <c r="A39" s="2">
-        <v>38</v>
-      </c>
-      <c r="B39" s="5"/>
+        <v>35</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>91</v>
+      </c>
       <c r="C39" s="4" t="s">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="D39" s="4" t="s">
-        <v>164</v>
+        <v>155</v>
       </c>
       <c r="E39" s="4" t="s">
-        <v>165</v>
-      </c>
-      <c r="F39" s="2" t="s">
-        <v>55</v>
-      </c>
+        <v>156</v>
+      </c>
+      <c r="F39" s="2"/>
       <c r="G39" s="2" t="s">
         <v>59</v>
       </c>
@@ -3460,21 +3387,19 @@
     </row>
     <row r="40" ht="31" spans="1:8">
       <c r="A40" s="2">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B40" s="5"/>
       <c r="C40" s="4" t="s">
-        <v>166</v>
+        <v>154</v>
       </c>
       <c r="D40" s="4" t="s">
-        <v>167</v>
+        <v>157</v>
       </c>
       <c r="E40" s="4" t="s">
-        <v>168</v>
-      </c>
-      <c r="F40" s="2" t="s">
-        <v>55</v>
-      </c>
+        <v>158</v>
+      </c>
+      <c r="F40" s="2"/>
       <c r="G40" s="2" t="s">
         <v>59</v>
       </c>
@@ -3482,21 +3407,19 @@
     </row>
     <row r="41" ht="31" spans="1:8">
       <c r="A41" s="2">
-        <v>40</v>
-      </c>
-      <c r="B41" s="6"/>
+        <v>37</v>
+      </c>
+      <c r="B41" s="5"/>
       <c r="C41" s="4" t="s">
-        <v>169</v>
+        <v>159</v>
       </c>
       <c r="D41" s="4" t="s">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="E41" s="4" t="s">
-        <v>171</v>
-      </c>
-      <c r="F41" s="2" t="s">
-        <v>55</v>
-      </c>
+        <v>161</v>
+      </c>
+      <c r="F41" s="2"/>
       <c r="G41" s="2" t="s">
         <v>59</v>
       </c>
@@ -3504,23 +3427,19 @@
     </row>
     <row r="42" ht="31" spans="1:8">
       <c r="A42" s="2">
-        <v>41</v>
-      </c>
-      <c r="B42" s="3" t="s">
-        <v>172</v>
-      </c>
+        <v>38</v>
+      </c>
+      <c r="B42" s="5"/>
       <c r="C42" s="4" t="s">
-        <v>173</v>
+        <v>159</v>
       </c>
       <c r="D42" s="4" t="s">
-        <v>174</v>
+        <v>162</v>
       </c>
       <c r="E42" s="4" t="s">
-        <v>175</v>
-      </c>
-      <c r="F42" s="2" t="s">
-        <v>55</v>
-      </c>
+        <v>163</v>
+      </c>
+      <c r="F42" s="2"/>
       <c r="G42" s="2" t="s">
         <v>59</v>
       </c>
@@ -3528,21 +3447,19 @@
     </row>
     <row r="43" ht="31" spans="1:8">
       <c r="A43" s="2">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B43" s="5"/>
       <c r="C43" s="4" t="s">
-        <v>176</v>
+        <v>164</v>
       </c>
       <c r="D43" s="4" t="s">
-        <v>177</v>
+        <v>165</v>
       </c>
       <c r="E43" s="4" t="s">
-        <v>178</v>
-      </c>
-      <c r="F43" s="2" t="s">
-        <v>55</v>
-      </c>
+        <v>166</v>
+      </c>
+      <c r="F43" s="2"/>
       <c r="G43" s="2" t="s">
         <v>59</v>
       </c>
@@ -3550,21 +3467,19 @@
     </row>
     <row r="44" ht="31" spans="1:8">
       <c r="A44" s="2">
-        <v>43</v>
-      </c>
-      <c r="B44" s="5"/>
+        <v>40</v>
+      </c>
+      <c r="B44" s="6"/>
       <c r="C44" s="4" t="s">
-        <v>179</v>
+        <v>167</v>
       </c>
       <c r="D44" s="4" t="s">
-        <v>180</v>
+        <v>168</v>
       </c>
       <c r="E44" s="4" t="s">
-        <v>181</v>
-      </c>
-      <c r="F44" s="2" t="s">
-        <v>55</v>
-      </c>
+        <v>169</v>
+      </c>
+      <c r="F44" s="2"/>
       <c r="G44" s="2" t="s">
         <v>59</v>
       </c>
@@ -3572,21 +3487,21 @@
     </row>
     <row r="45" ht="31" spans="1:8">
       <c r="A45" s="2">
-        <v>44</v>
-      </c>
-      <c r="B45" s="6"/>
+        <v>41</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>170</v>
+      </c>
       <c r="C45" s="4" t="s">
-        <v>182</v>
+        <v>171</v>
       </c>
       <c r="D45" s="4" t="s">
-        <v>183</v>
+        <v>172</v>
       </c>
       <c r="E45" s="4" t="s">
-        <v>184</v>
-      </c>
-      <c r="F45" s="2" t="s">
-        <v>55</v>
-      </c>
+        <v>173</v>
+      </c>
+      <c r="F45" s="2"/>
       <c r="G45" s="2" t="s">
         <v>59</v>
       </c>
@@ -3594,23 +3509,19 @@
     </row>
     <row r="46" ht="31" spans="1:8">
       <c r="A46" s="2">
-        <v>45</v>
-      </c>
-      <c r="B46" s="3" t="s">
-        <v>185</v>
-      </c>
+        <v>42</v>
+      </c>
+      <c r="B46" s="5"/>
       <c r="C46" s="4" t="s">
-        <v>186</v>
+        <v>174</v>
       </c>
       <c r="D46" s="4" t="s">
-        <v>187</v>
+        <v>175</v>
       </c>
       <c r="E46" s="4" t="s">
-        <v>188</v>
-      </c>
-      <c r="F46" s="2" t="s">
-        <v>55</v>
-      </c>
+        <v>176</v>
+      </c>
+      <c r="F46" s="2"/>
       <c r="G46" s="2" t="s">
         <v>59</v>
       </c>
@@ -3618,21 +3529,19 @@
     </row>
     <row r="47" ht="31" spans="1:8">
       <c r="A47" s="2">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="B47" s="5"/>
       <c r="C47" s="4" t="s">
-        <v>189</v>
+        <v>177</v>
       </c>
       <c r="D47" s="4" t="s">
-        <v>190</v>
+        <v>178</v>
       </c>
       <c r="E47" s="4" t="s">
-        <v>191</v>
-      </c>
-      <c r="F47" s="2" t="s">
-        <v>55</v>
-      </c>
+        <v>179</v>
+      </c>
+      <c r="F47" s="2"/>
       <c r="G47" s="2" t="s">
         <v>59</v>
       </c>
@@ -3640,21 +3549,19 @@
     </row>
     <row r="48" ht="31" spans="1:8">
       <c r="A48" s="2">
-        <v>47</v>
-      </c>
-      <c r="B48" s="5"/>
+        <v>44</v>
+      </c>
+      <c r="B48" s="6"/>
       <c r="C48" s="4" t="s">
-        <v>192</v>
+        <v>180</v>
       </c>
       <c r="D48" s="4" t="s">
-        <v>193</v>
+        <v>181</v>
       </c>
       <c r="E48" s="4" t="s">
-        <v>194</v>
-      </c>
-      <c r="F48" s="2" t="s">
-        <v>55</v>
-      </c>
+        <v>182</v>
+      </c>
+      <c r="F48" s="2"/>
       <c r="G48" s="2" t="s">
         <v>59</v>
       </c>
@@ -3662,21 +3569,21 @@
     </row>
     <row r="49" ht="31" spans="1:8">
       <c r="A49" s="2">
-        <v>48</v>
-      </c>
-      <c r="B49" s="6"/>
+        <v>45</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>183</v>
+      </c>
       <c r="C49" s="4" t="s">
-        <v>192</v>
+        <v>184</v>
       </c>
       <c r="D49" s="4" t="s">
-        <v>195</v>
+        <v>185</v>
       </c>
       <c r="E49" s="4" t="s">
-        <v>196</v>
-      </c>
-      <c r="F49" s="2" t="s">
-        <v>55</v>
-      </c>
+        <v>186</v>
+      </c>
+      <c r="F49" s="2"/>
       <c r="G49" s="2" t="s">
         <v>59</v>
       </c>
@@ -3684,157 +3591,143 @@
     </row>
     <row r="50" ht="31" spans="1:8">
       <c r="A50" s="2">
+        <v>46</v>
+      </c>
+      <c r="B50" s="5"/>
+      <c r="C50" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="D50" s="4" t="s">
+        <v>188</v>
+      </c>
+      <c r="E50" s="4" t="s">
+        <v>189</v>
+      </c>
+      <c r="F50" s="2"/>
+      <c r="G50" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="H50" s="4"/>
+    </row>
+    <row r="51" ht="31" spans="1:8">
+      <c r="A51" s="2">
+        <v>47</v>
+      </c>
+      <c r="B51" s="5"/>
+      <c r="C51" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="D51" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="E51" s="4" t="s">
+        <v>192</v>
+      </c>
+      <c r="F51" s="2"/>
+      <c r="G51" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="H51" s="4"/>
+    </row>
+    <row r="52" ht="31" spans="1:8">
+      <c r="A52" s="2">
+        <v>48</v>
+      </c>
+      <c r="B52" s="6"/>
+      <c r="C52" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="D52" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="E52" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="F52" s="2"/>
+      <c r="G52" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="H52" s="4"/>
+    </row>
+    <row r="53" ht="31" spans="1:8">
+      <c r="A53" s="2">
         <v>49</v>
       </c>
-      <c r="B50" s="3" t="s">
+      <c r="B53" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="C53" s="4" t="s">
+        <v>196</v>
+      </c>
+      <c r="D53" s="4" t="s">
         <v>197</v>
       </c>
-      <c r="C50" s="4" t="s">
+      <c r="E53" s="4" t="s">
         <v>198</v>
       </c>
-      <c r="D50" s="4" t="s">
+      <c r="F53" s="2"/>
+      <c r="G53" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="H53" s="4"/>
+    </row>
+    <row r="54" ht="46" spans="1:8">
+      <c r="A54" s="2">
+        <v>50</v>
+      </c>
+      <c r="B54" s="6"/>
+      <c r="C54" s="4" t="s">
         <v>199</v>
       </c>
-      <c r="E50" s="4" t="s">
+      <c r="D54" s="4" t="s">
         <v>200</v>
       </c>
-      <c r="F50" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="G50" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="H50" s="4"/>
-    </row>
-    <row r="51" ht="46" spans="1:8">
-      <c r="A51" s="2">
-        <v>50</v>
-      </c>
-      <c r="B51" s="6"/>
-      <c r="C51" s="4" t="s">
+      <c r="E54" s="4" t="s">
         <v>201</v>
       </c>
-      <c r="D51" s="4" t="s">
+      <c r="F54" s="2"/>
+      <c r="G54" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="H54" s="4"/>
+    </row>
+    <row r="55" ht="46" spans="1:8">
+      <c r="A55" s="2">
+        <v>51</v>
+      </c>
+      <c r="B55" s="3" t="s">
         <v>202</v>
       </c>
-      <c r="E51" s="4" t="s">
+      <c r="C55" s="4" t="s">
         <v>203</v>
       </c>
-      <c r="F51" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="G51" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="H51" s="4"/>
-    </row>
-    <row r="52" ht="46" spans="1:8">
-      <c r="A52" s="2">
-        <v>51</v>
-      </c>
-      <c r="B52" s="3" t="s">
+      <c r="D55" s="4" t="s">
         <v>204</v>
       </c>
-      <c r="C52" s="4" t="s">
+      <c r="E55" s="4" t="s">
         <v>205</v>
       </c>
-      <c r="D52" s="4" t="s">
+      <c r="F55" s="2"/>
+      <c r="G55" s="2" t="s">
         <v>206</v>
       </c>
-      <c r="E52" s="4" t="s">
-        <v>207</v>
-      </c>
-      <c r="F52" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="G52" s="2" t="s">
-        <v>208</v>
-      </c>
-      <c r="H52" s="4"/>
-    </row>
-    <row r="53" ht="46" spans="1:8">
-      <c r="A53" s="2">
+      <c r="H55" s="4"/>
+    </row>
+    <row r="56" ht="46" spans="1:8">
+      <c r="A56" s="2">
         <v>52</v>
-      </c>
-      <c r="B53" s="5"/>
-      <c r="C53" s="4" t="s">
-        <v>209</v>
-      </c>
-      <c r="D53" s="4" t="s">
-        <v>210</v>
-      </c>
-      <c r="E53" s="4" t="s">
-        <v>211</v>
-      </c>
-      <c r="F53" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="G53" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="H53" s="4"/>
-    </row>
-    <row r="54" ht="31" spans="1:8">
-      <c r="A54" s="2">
-        <v>53</v>
-      </c>
-      <c r="B54" s="5"/>
-      <c r="C54" s="4" t="s">
-        <v>212</v>
-      </c>
-      <c r="D54" s="4" t="s">
-        <v>213</v>
-      </c>
-      <c r="E54" s="4" t="s">
-        <v>214</v>
-      </c>
-      <c r="F54" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="G54" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="H54" s="4"/>
-    </row>
-    <row r="55" ht="31" spans="1:8">
-      <c r="A55" s="2">
-        <v>54</v>
-      </c>
-      <c r="B55" s="5"/>
-      <c r="C55" s="4" t="s">
-        <v>215</v>
-      </c>
-      <c r="D55" s="4" t="s">
-        <v>216</v>
-      </c>
-      <c r="E55" s="4" t="s">
-        <v>217</v>
-      </c>
-      <c r="F55" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="G55" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="H55" s="4"/>
-    </row>
-    <row r="56" ht="31" spans="1:8">
-      <c r="A56" s="2">
-        <v>55</v>
       </c>
       <c r="B56" s="5"/>
       <c r="C56" s="4" t="s">
-        <v>218</v>
+        <v>207</v>
       </c>
       <c r="D56" s="4" t="s">
-        <v>219</v>
+        <v>208</v>
       </c>
       <c r="E56" s="4" t="s">
-        <v>220</v>
-      </c>
-      <c r="F56" s="2" t="s">
-        <v>55</v>
-      </c>
+        <v>209</v>
+      </c>
+      <c r="F56" s="2"/>
       <c r="G56" s="2" t="s">
         <v>59</v>
       </c>
@@ -3842,21 +3735,19 @@
     </row>
     <row r="57" ht="31" spans="1:8">
       <c r="A57" s="2">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="B57" s="5"/>
       <c r="C57" s="4" t="s">
-        <v>221</v>
+        <v>210</v>
       </c>
       <c r="D57" s="4" t="s">
-        <v>222</v>
+        <v>211</v>
       </c>
       <c r="E57" s="4" t="s">
-        <v>223</v>
-      </c>
-      <c r="F57" s="2" t="s">
-        <v>55</v>
-      </c>
+        <v>212</v>
+      </c>
+      <c r="F57" s="2"/>
       <c r="G57" s="2" t="s">
         <v>59</v>
       </c>
@@ -3864,21 +3755,19 @@
     </row>
     <row r="58" ht="31" spans="1:8">
       <c r="A58" s="2">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="B58" s="5"/>
       <c r="C58" s="4" t="s">
-        <v>224</v>
+        <v>213</v>
       </c>
       <c r="D58" s="4" t="s">
-        <v>225</v>
+        <v>214</v>
       </c>
       <c r="E58" s="4" t="s">
-        <v>226</v>
-      </c>
-      <c r="F58" s="2" t="s">
-        <v>55</v>
-      </c>
+        <v>215</v>
+      </c>
+      <c r="F58" s="2"/>
       <c r="G58" s="2" t="s">
         <v>59</v>
       </c>
@@ -3886,21 +3775,19 @@
     </row>
     <row r="59" ht="31" spans="1:8">
       <c r="A59" s="2">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="B59" s="5"/>
       <c r="C59" s="4" t="s">
-        <v>227</v>
+        <v>216</v>
       </c>
       <c r="D59" s="4" t="s">
-        <v>228</v>
+        <v>217</v>
       </c>
       <c r="E59" s="4" t="s">
-        <v>229</v>
-      </c>
-      <c r="F59" s="2" t="s">
-        <v>55</v>
-      </c>
+        <v>218</v>
+      </c>
+      <c r="F59" s="2"/>
       <c r="G59" s="2" t="s">
         <v>59</v>
       </c>
@@ -3908,21 +3795,19 @@
     </row>
     <row r="60" ht="31" spans="1:8">
       <c r="A60" s="2">
-        <v>59</v>
-      </c>
-      <c r="B60" s="6"/>
+        <v>56</v>
+      </c>
+      <c r="B60" s="5"/>
       <c r="C60" s="4" t="s">
-        <v>230</v>
+        <v>219</v>
       </c>
       <c r="D60" s="4" t="s">
-        <v>231</v>
+        <v>220</v>
       </c>
       <c r="E60" s="4" t="s">
-        <v>232</v>
-      </c>
-      <c r="F60" s="2" t="s">
-        <v>55</v>
-      </c>
+        <v>221</v>
+      </c>
+      <c r="F60" s="2"/>
       <c r="G60" s="2" t="s">
         <v>59</v>
       </c>
@@ -3930,44 +3815,102 @@
     </row>
     <row r="61" ht="31" spans="1:8">
       <c r="A61" s="2">
+        <v>57</v>
+      </c>
+      <c r="B61" s="5"/>
+      <c r="C61" s="4" t="s">
+        <v>222</v>
+      </c>
+      <c r="D61" s="4" t="s">
+        <v>223</v>
+      </c>
+      <c r="E61" s="4" t="s">
+        <v>224</v>
+      </c>
+      <c r="F61" s="2"/>
+      <c r="G61" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="H61" s="4"/>
+    </row>
+    <row r="62" ht="31" spans="1:8">
+      <c r="A62" s="2">
+        <v>58</v>
+      </c>
+      <c r="B62" s="5"/>
+      <c r="C62" s="4" t="s">
+        <v>225</v>
+      </c>
+      <c r="D62" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="E62" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="F62" s="2"/>
+      <c r="G62" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="H62" s="4"/>
+    </row>
+    <row r="63" ht="31" spans="1:8">
+      <c r="A63" s="2">
+        <v>59</v>
+      </c>
+      <c r="B63" s="6"/>
+      <c r="C63" s="4" t="s">
+        <v>228</v>
+      </c>
+      <c r="D63" s="4" t="s">
+        <v>229</v>
+      </c>
+      <c r="E63" s="4" t="s">
+        <v>230</v>
+      </c>
+      <c r="F63" s="2"/>
+      <c r="G63" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="H63" s="4"/>
+    </row>
+    <row r="64" ht="31" spans="1:8">
+      <c r="A64" s="2">
         <v>60</v>
       </c>
-      <c r="B61" s="3" t="s">
+      <c r="B64" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="C64" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="D64" s="4" t="s">
         <v>233</v>
       </c>
-      <c r="C61" s="4" t="s">
+      <c r="E64" s="4" t="s">
         <v>234</v>
       </c>
-      <c r="D61" s="4" t="s">
+      <c r="F64" s="8"/>
+      <c r="G64" s="2" t="s">
         <v>235</v>
       </c>
-      <c r="E61" s="4" t="s">
-        <v>236</v>
-      </c>
-      <c r="F61" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="G61" s="2" t="s">
-        <v>237</v>
-      </c>
-      <c r="H61" s="4"/>
+      <c r="H64" s="4"/>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:I61" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:I64" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <mergeCells count="11">
     <mergeCell ref="B2:B10"/>
-    <mergeCell ref="B11:B17"/>
-    <mergeCell ref="B18:B26"/>
-    <mergeCell ref="B27:B29"/>
+    <mergeCell ref="B11:B20"/>
+    <mergeCell ref="B21:B29"/>
     <mergeCell ref="B30:B32"/>
     <mergeCell ref="B33:B35"/>
-    <mergeCell ref="B36:B41"/>
-    <mergeCell ref="B42:B45"/>
-    <mergeCell ref="B46:B49"/>
-    <mergeCell ref="B50:B51"/>
-    <mergeCell ref="B52:B60"/>
+    <mergeCell ref="B36:B38"/>
+    <mergeCell ref="B39:B44"/>
+    <mergeCell ref="B45:B48"/>
+    <mergeCell ref="B49:B52"/>
+    <mergeCell ref="B53:B54"/>
+    <mergeCell ref="B55:B63"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
@@ -4023,16 +3966,16 @@
         <v>52</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="E2" s="4" t="s">
+        <v>237</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="G2" s="2" t="s">
         <v>239</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>240</v>
       </c>
     </row>
     <row r="3" ht="36" customHeight="1" spans="1:7">
@@ -4041,16 +3984,16 @@
       </c>
       <c r="B3" s="5"/>
       <c r="C3" s="4" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D3" s="4" t="s">
+        <v>240</v>
+      </c>
+      <c r="E3" s="4" t="s">
         <v>241</v>
       </c>
-      <c r="E3" s="4" t="s">
-        <v>242</v>
-      </c>
       <c r="F3" s="2" t="s">
-        <v>55</v>
+        <v>238</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>59</v>
@@ -4062,16 +4005,16 @@
       </c>
       <c r="B4" s="6"/>
       <c r="C4" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="D4" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="D4" s="4" t="s">
-        <v>76</v>
-      </c>
       <c r="E4" s="4" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>55</v>
+        <v>238</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>59</v>
@@ -4082,19 +4025,19 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="C5" s="4" t="s">
         <v>244</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="D5" s="4" t="s">
         <v>245</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="E5" s="4" t="s">
         <v>246</v>
       </c>
-      <c r="E5" s="4" t="s">
-        <v>247</v>
-      </c>
       <c r="F5" s="2" t="s">
-        <v>55</v>
+        <v>238</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>59</v>
@@ -4106,16 +4049,16 @@
       </c>
       <c r="B6" s="5"/>
       <c r="C6" s="4" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="D6" s="4" t="s">
+        <v>247</v>
+      </c>
+      <c r="E6" s="4" t="s">
         <v>248</v>
       </c>
-      <c r="E6" s="4" t="s">
-        <v>249</v>
-      </c>
       <c r="F6" s="2" t="s">
-        <v>55</v>
+        <v>238</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>59</v>
@@ -4127,16 +4070,16 @@
       </c>
       <c r="B7" s="6"/>
       <c r="C7" s="4" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="D7" s="4" t="s">
+        <v>249</v>
+      </c>
+      <c r="E7" s="4" t="s">
         <v>250</v>
       </c>
-      <c r="E7" s="4" t="s">
-        <v>251</v>
-      </c>
       <c r="F7" s="2" t="s">
-        <v>55</v>
+        <v>238</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>59</v>
@@ -4147,19 +4090,19 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="C8" s="4" t="s">
         <v>252</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="D8" s="4" t="s">
         <v>253</v>
       </c>
-      <c r="D8" s="4" t="s">
+      <c r="E8" s="4" t="s">
         <v>254</v>
       </c>
-      <c r="E8" s="4" t="s">
-        <v>255</v>
-      </c>
       <c r="F8" s="2" t="s">
-        <v>55</v>
+        <v>238</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>59</v>
@@ -4171,16 +4114,16 @@
       </c>
       <c r="B9" s="5"/>
       <c r="C9" s="4" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="D9" s="4" t="s">
+        <v>255</v>
+      </c>
+      <c r="E9" s="4" t="s">
         <v>256</v>
       </c>
-      <c r="E9" s="4" t="s">
-        <v>257</v>
-      </c>
       <c r="F9" s="2" t="s">
-        <v>55</v>
+        <v>238</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>59</v>
@@ -4192,16 +4135,16 @@
       </c>
       <c r="B10" s="5"/>
       <c r="C10" s="4" t="s">
+        <v>257</v>
+      </c>
+      <c r="D10" s="4" t="s">
         <v>258</v>
       </c>
-      <c r="D10" s="4" t="s">
+      <c r="E10" s="4" t="s">
         <v>259</v>
       </c>
-      <c r="E10" s="4" t="s">
-        <v>260</v>
-      </c>
       <c r="F10" s="2" t="s">
-        <v>55</v>
+        <v>238</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>59</v>
@@ -4213,16 +4156,16 @@
       </c>
       <c r="B11" s="6"/>
       <c r="C11" s="4" t="s">
+        <v>260</v>
+      </c>
+      <c r="D11" s="4" t="s">
         <v>261</v>
       </c>
-      <c r="D11" s="4" t="s">
+      <c r="E11" s="4" t="s">
         <v>262</v>
       </c>
-      <c r="E11" s="4" t="s">
-        <v>263</v>
-      </c>
       <c r="F11" s="2" t="s">
-        <v>55</v>
+        <v>238</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>59</v>
@@ -4233,19 +4176,19 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="C12" s="4" t="s">
         <v>264</v>
       </c>
-      <c r="C12" s="4" t="s">
+      <c r="D12" s="4" t="s">
         <v>265</v>
       </c>
-      <c r="D12" s="4" t="s">
+      <c r="E12" s="4" t="s">
         <v>266</v>
       </c>
-      <c r="E12" s="4" t="s">
-        <v>267</v>
-      </c>
       <c r="F12" s="2" t="s">
-        <v>55</v>
+        <v>238</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>59</v>
@@ -4257,16 +4200,16 @@
       </c>
       <c r="B13" s="6"/>
       <c r="C13" s="4" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="D13" s="4" t="s">
+        <v>267</v>
+      </c>
+      <c r="E13" s="4" t="s">
         <v>268</v>
       </c>
-      <c r="E13" s="4" t="s">
-        <v>269</v>
-      </c>
       <c r="F13" s="2" t="s">
-        <v>55</v>
+        <v>238</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>59</v>
@@ -4277,19 +4220,19 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="C14" s="4" t="s">
         <v>270</v>
       </c>
-      <c r="C14" s="4" t="s">
+      <c r="D14" s="4" t="s">
         <v>271</v>
       </c>
-      <c r="D14" s="4" t="s">
+      <c r="E14" s="4" t="s">
         <v>272</v>
       </c>
-      <c r="E14" s="4" t="s">
-        <v>273</v>
-      </c>
       <c r="F14" s="2" t="s">
-        <v>55</v>
+        <v>238</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>59</v>
@@ -4301,16 +4244,16 @@
       </c>
       <c r="B15" s="5"/>
       <c r="C15" s="4" t="s">
+        <v>273</v>
+      </c>
+      <c r="D15" s="4" t="s">
         <v>274</v>
       </c>
-      <c r="D15" s="4" t="s">
+      <c r="E15" s="4" t="s">
         <v>275</v>
       </c>
-      <c r="E15" s="4" t="s">
-        <v>276</v>
-      </c>
       <c r="F15" s="2" t="s">
-        <v>55</v>
+        <v>238</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>59</v>
@@ -4322,19 +4265,19 @@
       </c>
       <c r="B16" s="6"/>
       <c r="C16" s="4" t="s">
+        <v>276</v>
+      </c>
+      <c r="D16" s="4" t="s">
         <v>277</v>
       </c>
-      <c r="D16" s="4" t="s">
+      <c r="E16" s="4" t="s">
         <v>278</v>
       </c>
-      <c r="E16" s="4" t="s">
+      <c r="F16" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="G16" s="2" t="s">
         <v>279</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="G16" s="2" t="s">
-        <v>280</v>
       </c>
     </row>
     <row r="17" ht="36" customHeight="1" spans="1:7">
@@ -4342,22 +4285,22 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="C17" s="4" t="s">
         <v>281</v>
       </c>
-      <c r="C17" s="4" t="s">
+      <c r="D17" s="4" t="s">
         <v>282</v>
       </c>
-      <c r="D17" s="4" t="s">
+      <c r="E17" s="4" t="s">
         <v>283</v>
       </c>
-      <c r="E17" s="4" t="s">
+      <c r="F17" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="G17" s="2" t="s">
         <v>284</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="G17" s="2" t="s">
-        <v>285</v>
       </c>
     </row>
     <row r="18" ht="36" customHeight="1" spans="1:7">
@@ -4366,16 +4309,16 @@
       </c>
       <c r="B18" s="6"/>
       <c r="C18" s="4" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="D18" s="4" t="s">
+        <v>285</v>
+      </c>
+      <c r="E18" s="4" t="s">
         <v>286</v>
       </c>
-      <c r="E18" s="4" t="s">
-        <v>287</v>
-      </c>
       <c r="F18" s="2" t="s">
-        <v>55</v>
+        <v>238</v>
       </c>
       <c r="G18" s="2" t="s">
         <v>59</v>
@@ -4386,19 +4329,19 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
+        <v>287</v>
+      </c>
+      <c r="C19" s="4" t="s">
         <v>288</v>
       </c>
-      <c r="C19" s="4" t="s">
+      <c r="D19" s="4" t="s">
         <v>289</v>
       </c>
-      <c r="D19" s="4" t="s">
+      <c r="E19" s="4" t="s">
         <v>290</v>
       </c>
-      <c r="E19" s="4" t="s">
-        <v>291</v>
-      </c>
       <c r="F19" s="2" t="s">
-        <v>55</v>
+        <v>238</v>
       </c>
       <c r="G19" s="2" t="s">
         <v>59</v>
@@ -4410,19 +4353,19 @@
       </c>
       <c r="B20" s="6"/>
       <c r="C20" s="4" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="D20" s="4" t="s">
+        <v>291</v>
+      </c>
+      <c r="E20" s="4" t="s">
         <v>292</v>
       </c>
-      <c r="E20" s="4" t="s">
+      <c r="F20" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="G20" s="2" t="s">
         <v>293</v>
-      </c>
-      <c r="F20" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="G20" s="2" t="s">
-        <v>294</v>
       </c>
     </row>
     <row r="21" ht="36" customHeight="1" spans="1:7">
@@ -4430,19 +4373,19 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
+        <v>294</v>
+      </c>
+      <c r="C21" s="4" t="s">
         <v>295</v>
       </c>
-      <c r="C21" s="4" t="s">
+      <c r="D21" s="4" t="s">
         <v>296</v>
       </c>
-      <c r="D21" s="4" t="s">
+      <c r="E21" s="4" t="s">
         <v>297</v>
       </c>
-      <c r="E21" s="4" t="s">
-        <v>298</v>
-      </c>
       <c r="F21" s="2" t="s">
-        <v>55</v>
+        <v>238</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>59</v>
@@ -4454,16 +4397,16 @@
       </c>
       <c r="B22" s="6"/>
       <c r="C22" s="4" t="s">
+        <v>298</v>
+      </c>
+      <c r="D22" s="4" t="s">
         <v>299</v>
       </c>
-      <c r="D22" s="4" t="s">
+      <c r="E22" s="4" t="s">
         <v>300</v>
       </c>
-      <c r="E22" s="4" t="s">
-        <v>301</v>
-      </c>
       <c r="F22" s="2" t="s">
-        <v>55</v>
+        <v>238</v>
       </c>
       <c r="G22" s="2" t="s">
         <v>59</v>
@@ -4474,22 +4417,22 @@
         <v>22</v>
       </c>
       <c r="B23" s="3" t="s">
+        <v>301</v>
+      </c>
+      <c r="C23" s="4" t="s">
         <v>302</v>
       </c>
-      <c r="C23" s="4" t="s">
+      <c r="D23" s="4" t="s">
         <v>303</v>
       </c>
-      <c r="D23" s="4" t="s">
+      <c r="E23" s="4" t="s">
         <v>304</v>
       </c>
-      <c r="E23" s="4" t="s">
+      <c r="F23" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="G23" s="2" t="s">
         <v>305</v>
-      </c>
-      <c r="F23" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="G23" s="2" t="s">
-        <v>306</v>
       </c>
     </row>
     <row r="24" ht="36" customHeight="1" spans="1:7">
@@ -4498,16 +4441,16 @@
       </c>
       <c r="B24" s="6"/>
       <c r="C24" s="4" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="D24" s="4" t="s">
+        <v>306</v>
+      </c>
+      <c r="E24" s="4" t="s">
         <v>307</v>
       </c>
-      <c r="E24" s="4" t="s">
-        <v>308</v>
-      </c>
       <c r="F24" s="2" t="s">
-        <v>55</v>
+        <v>238</v>
       </c>
       <c r="G24" s="2" t="s">
         <v>59</v>
@@ -4579,13 +4522,13 @@
         <v>52</v>
       </c>
       <c r="D2" s="4" t="s">
+        <v>308</v>
+      </c>
+      <c r="E2" s="4" t="s">
         <v>309</v>
       </c>
-      <c r="E2" s="4" t="s">
-        <v>310</v>
-      </c>
       <c r="F2" s="2" t="s">
-        <v>55</v>
+        <v>238</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>59</v>
@@ -4597,16 +4540,16 @@
       </c>
       <c r="B3" s="5"/>
       <c r="C3" s="4" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D3" s="4" t="s">
+        <v>310</v>
+      </c>
+      <c r="E3" s="4" t="s">
         <v>311</v>
       </c>
-      <c r="E3" s="4" t="s">
-        <v>312</v>
-      </c>
       <c r="F3" s="2" t="s">
-        <v>55</v>
+        <v>238</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>59</v>
@@ -4618,16 +4561,16 @@
       </c>
       <c r="B4" s="6"/>
       <c r="C4" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="D4" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="D4" s="4" t="s">
-        <v>76</v>
-      </c>
       <c r="E4" s="4" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>55</v>
+        <v>238</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>59</v>
@@ -4638,22 +4581,22 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="C5" s="4" t="s">
         <v>314</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="D5" s="4" t="s">
         <v>315</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="E5" s="4" t="s">
         <v>316</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="F5" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="G5" s="2" t="s">
         <v>317</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>318</v>
       </c>
     </row>
     <row r="6" ht="31" spans="1:7">
@@ -4662,16 +4605,16 @@
       </c>
       <c r="B6" s="6"/>
       <c r="C6" s="4" t="s">
+        <v>318</v>
+      </c>
+      <c r="D6" s="4" t="s">
         <v>319</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="E6" s="4" t="s">
         <v>320</v>
       </c>
-      <c r="E6" s="4" t="s">
-        <v>321</v>
-      </c>
       <c r="F6" s="2" t="s">
-        <v>55</v>
+        <v>238</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>59</v>
@@ -4682,19 +4625,19 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
+        <v>321</v>
+      </c>
+      <c r="C7" s="4" t="s">
         <v>322</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="D7" s="4" t="s">
         <v>323</v>
       </c>
-      <c r="D7" s="4" t="s">
+      <c r="E7" s="4" t="s">
         <v>324</v>
       </c>
-      <c r="E7" s="4" t="s">
-        <v>325</v>
-      </c>
       <c r="F7" s="2" t="s">
-        <v>55</v>
+        <v>238</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>59</v>
@@ -4706,16 +4649,16 @@
       </c>
       <c r="B8" s="5"/>
       <c r="C8" s="4" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="D8" s="4" t="s">
+        <v>325</v>
+      </c>
+      <c r="E8" s="4" t="s">
         <v>326</v>
       </c>
-      <c r="E8" s="4" t="s">
-        <v>327</v>
-      </c>
       <c r="F8" s="2" t="s">
-        <v>55</v>
+        <v>238</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>59</v>
@@ -4727,16 +4670,16 @@
       </c>
       <c r="B9" s="6"/>
       <c r="C9" s="4" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="D9" s="4" t="s">
+        <v>327</v>
+      </c>
+      <c r="E9" s="4" t="s">
         <v>328</v>
       </c>
-      <c r="E9" s="4" t="s">
-        <v>329</v>
-      </c>
       <c r="F9" s="2" t="s">
-        <v>55</v>
+        <v>238</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>59</v>
@@ -4747,19 +4690,19 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
+        <v>329</v>
+      </c>
+      <c r="C10" s="4" t="s">
         <v>330</v>
       </c>
-      <c r="C10" s="4" t="s">
+      <c r="D10" s="4" t="s">
         <v>331</v>
       </c>
-      <c r="D10" s="4" t="s">
+      <c r="E10" s="4" t="s">
         <v>332</v>
       </c>
-      <c r="E10" s="4" t="s">
-        <v>333</v>
-      </c>
       <c r="F10" s="2" t="s">
-        <v>55</v>
+        <v>238</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>59</v>
@@ -4771,16 +4714,16 @@
       </c>
       <c r="B11" s="5"/>
       <c r="C11" s="4" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D11" s="4" t="s">
+        <v>333</v>
+      </c>
+      <c r="E11" s="4" t="s">
         <v>334</v>
       </c>
-      <c r="E11" s="4" t="s">
-        <v>335</v>
-      </c>
       <c r="F11" s="2" t="s">
-        <v>55</v>
+        <v>238</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>59</v>
@@ -4792,16 +4735,16 @@
       </c>
       <c r="B12" s="5"/>
       <c r="C12" s="4" t="s">
+        <v>335</v>
+      </c>
+      <c r="D12" s="4" t="s">
         <v>336</v>
       </c>
-      <c r="D12" s="4" t="s">
+      <c r="E12" s="4" t="s">
         <v>337</v>
       </c>
-      <c r="E12" s="4" t="s">
-        <v>338</v>
-      </c>
       <c r="F12" s="2" t="s">
-        <v>55</v>
+        <v>238</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>59</v>
@@ -4813,16 +4756,16 @@
       </c>
       <c r="B13" s="5"/>
       <c r="C13" s="4" t="s">
+        <v>338</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>336</v>
+      </c>
+      <c r="E13" s="4" t="s">
         <v>339</v>
       </c>
-      <c r="D13" s="4" t="s">
-        <v>337</v>
-      </c>
-      <c r="E13" s="4" t="s">
-        <v>340</v>
-      </c>
       <c r="F13" s="2" t="s">
-        <v>55</v>
+        <v>238</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>59</v>
@@ -4834,16 +4777,16 @@
       </c>
       <c r="B14" s="6"/>
       <c r="C14" s="4" t="s">
+        <v>340</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>336</v>
+      </c>
+      <c r="E14" s="4" t="s">
         <v>341</v>
       </c>
-      <c r="D14" s="4" t="s">
-        <v>337</v>
-      </c>
-      <c r="E14" s="4" t="s">
-        <v>342</v>
-      </c>
       <c r="F14" s="2" t="s">
-        <v>55</v>
+        <v>238</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>59</v>
@@ -4854,19 +4797,19 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="C15" s="4" t="s">
+        <v>342</v>
+      </c>
+      <c r="D15" s="4" t="s">
         <v>343</v>
       </c>
-      <c r="D15" s="4" t="s">
+      <c r="E15" s="4" t="s">
         <v>344</v>
       </c>
-      <c r="E15" s="4" t="s">
-        <v>345</v>
-      </c>
       <c r="F15" s="2" t="s">
-        <v>55</v>
+        <v>238</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>59</v>
@@ -4878,16 +4821,16 @@
       </c>
       <c r="B16" s="5"/>
       <c r="C16" s="4" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="D16" s="4" t="s">
+        <v>345</v>
+      </c>
+      <c r="E16" s="4" t="s">
         <v>346</v>
       </c>
-      <c r="E16" s="4" t="s">
-        <v>347</v>
-      </c>
       <c r="F16" s="2" t="s">
-        <v>55</v>
+        <v>238</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>59</v>
@@ -4899,16 +4842,16 @@
       </c>
       <c r="B17" s="5"/>
       <c r="C17" s="4" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="D17" s="4" t="s">
+        <v>347</v>
+      </c>
+      <c r="E17" s="4" t="s">
         <v>348</v>
       </c>
-      <c r="E17" s="4" t="s">
-        <v>349</v>
-      </c>
       <c r="F17" s="2" t="s">
-        <v>55</v>
+        <v>238</v>
       </c>
       <c r="G17" s="2" t="s">
         <v>59</v>
@@ -4920,16 +4863,16 @@
       </c>
       <c r="B18" s="5"/>
       <c r="C18" s="4" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="D18" s="4" t="s">
+        <v>349</v>
+      </c>
+      <c r="E18" s="4" t="s">
         <v>350</v>
       </c>
-      <c r="E18" s="4" t="s">
-        <v>351</v>
-      </c>
       <c r="F18" s="2" t="s">
-        <v>55</v>
+        <v>238</v>
       </c>
       <c r="G18" s="2" t="s">
         <v>59</v>
@@ -4941,16 +4884,16 @@
       </c>
       <c r="B19" s="5"/>
       <c r="C19" s="4" t="s">
+        <v>351</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>343</v>
+      </c>
+      <c r="E19" s="4" t="s">
         <v>352</v>
       </c>
-      <c r="D19" s="4" t="s">
-        <v>344</v>
-      </c>
-      <c r="E19" s="4" t="s">
-        <v>353</v>
-      </c>
       <c r="F19" s="2" t="s">
-        <v>55</v>
+        <v>238</v>
       </c>
       <c r="G19" s="2" t="s">
         <v>59</v>
@@ -4962,16 +4905,16 @@
       </c>
       <c r="B20" s="5"/>
       <c r="C20" s="4" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="D20" s="4" t="s">
+        <v>353</v>
+      </c>
+      <c r="E20" s="4" t="s">
         <v>354</v>
       </c>
-      <c r="E20" s="4" t="s">
-        <v>355</v>
-      </c>
       <c r="F20" s="2" t="s">
-        <v>55</v>
+        <v>238</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>59</v>
@@ -4983,16 +4926,16 @@
       </c>
       <c r="B21" s="6"/>
       <c r="C21" s="4" t="s">
+        <v>355</v>
+      </c>
+      <c r="D21" s="4" t="s">
         <v>356</v>
       </c>
-      <c r="D21" s="4" t="s">
+      <c r="E21" s="4" t="s">
         <v>357</v>
       </c>
-      <c r="E21" s="4" t="s">
-        <v>358</v>
-      </c>
       <c r="F21" s="2" t="s">
-        <v>55</v>
+        <v>238</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>59</v>
@@ -5003,19 +4946,19 @@
         <v>21</v>
       </c>
       <c r="B22" s="3" t="s">
+        <v>358</v>
+      </c>
+      <c r="C22" s="4" t="s">
         <v>359</v>
       </c>
-      <c r="C22" s="4" t="s">
+      <c r="D22" s="4" t="s">
+        <v>356</v>
+      </c>
+      <c r="E22" s="4" t="s">
         <v>360</v>
       </c>
-      <c r="D22" s="4" t="s">
-        <v>357</v>
-      </c>
-      <c r="E22" s="4" t="s">
-        <v>361</v>
-      </c>
       <c r="F22" s="2" t="s">
-        <v>55</v>
+        <v>238</v>
       </c>
       <c r="G22" s="2" t="s">
         <v>59</v>
@@ -5026,19 +4969,19 @@
         <v>22</v>
       </c>
       <c r="B23" s="3" t="s">
+        <v>361</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>183</v>
+      </c>
+      <c r="D23" s="4" t="s">
+        <v>356</v>
+      </c>
+      <c r="E23" s="4" t="s">
         <v>362</v>
       </c>
-      <c r="C23" s="4" t="s">
-        <v>185</v>
-      </c>
-      <c r="D23" s="4" t="s">
-        <v>357</v>
-      </c>
-      <c r="E23" s="4" t="s">
-        <v>363</v>
-      </c>
       <c r="F23" s="2" t="s">
-        <v>55</v>
+        <v>238</v>
       </c>
       <c r="G23" s="2" t="s">
         <v>59</v>
@@ -5050,16 +4993,16 @@
       </c>
       <c r="B24" s="5"/>
       <c r="C24" s="4" t="s">
+        <v>363</v>
+      </c>
+      <c r="D24" s="4" t="s">
         <v>364</v>
       </c>
-      <c r="D24" s="4" t="s">
+      <c r="E24" s="4" t="s">
         <v>365</v>
       </c>
-      <c r="E24" s="4" t="s">
-        <v>366</v>
-      </c>
       <c r="F24" s="2" t="s">
-        <v>55</v>
+        <v>238</v>
       </c>
       <c r="G24" s="2" t="s">
         <v>59</v>
@@ -5071,16 +5014,16 @@
       </c>
       <c r="B25" s="5"/>
       <c r="C25" s="4" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="D25" s="4" t="s">
+        <v>366</v>
+      </c>
+      <c r="E25" s="4" t="s">
         <v>367</v>
       </c>
-      <c r="E25" s="4" t="s">
-        <v>368</v>
-      </c>
       <c r="F25" s="2" t="s">
-        <v>55</v>
+        <v>238</v>
       </c>
       <c r="G25" s="2" t="s">
         <v>59</v>
@@ -5092,16 +5035,16 @@
       </c>
       <c r="B26" s="6"/>
       <c r="C26" s="4" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>55</v>
+        <v>238</v>
       </c>
       <c r="G26" s="2" t="s">
         <v>59</v>
@@ -5112,19 +5055,19 @@
         <v>26</v>
       </c>
       <c r="B27" s="3" t="s">
+        <v>369</v>
+      </c>
+      <c r="C27" s="4" t="s">
         <v>370</v>
       </c>
-      <c r="C27" s="4" t="s">
+      <c r="D27" s="4" t="s">
         <v>371</v>
       </c>
-      <c r="D27" s="4" t="s">
+      <c r="E27" s="4" t="s">
         <v>372</v>
       </c>
-      <c r="E27" s="4" t="s">
-        <v>373</v>
-      </c>
       <c r="F27" s="2" t="s">
-        <v>55</v>
+        <v>238</v>
       </c>
       <c r="G27" s="2" t="s">
         <v>59</v>
@@ -5135,19 +5078,19 @@
         <v>27</v>
       </c>
       <c r="B28" s="3" t="s">
+        <v>373</v>
+      </c>
+      <c r="C28" s="4" t="s">
         <v>374</v>
       </c>
-      <c r="C28" s="4" t="s">
+      <c r="D28" s="4" t="s">
         <v>375</v>
       </c>
-      <c r="D28" s="4" t="s">
+      <c r="E28" s="4" t="s">
         <v>376</v>
       </c>
-      <c r="E28" s="4" t="s">
-        <v>377</v>
-      </c>
       <c r="F28" s="2" t="s">
-        <v>55</v>
+        <v>238</v>
       </c>
       <c r="G28" s="2" t="s">
         <v>59</v>
@@ -5158,19 +5101,19 @@
         <v>28</v>
       </c>
       <c r="B29" s="3" t="s">
+        <v>377</v>
+      </c>
+      <c r="C29" s="4" t="s">
         <v>378</v>
       </c>
-      <c r="C29" s="4" t="s">
+      <c r="D29" s="4" t="s">
         <v>379</v>
       </c>
-      <c r="D29" s="4" t="s">
+      <c r="E29" s="4" t="s">
         <v>380</v>
       </c>
-      <c r="E29" s="4" t="s">
-        <v>381</v>
-      </c>
       <c r="F29" s="2" t="s">
-        <v>55</v>
+        <v>238</v>
       </c>
       <c r="G29" s="2" t="s">
         <v>59</v>
@@ -5181,19 +5124,19 @@
         <v>29</v>
       </c>
       <c r="B30" s="3" t="s">
+        <v>381</v>
+      </c>
+      <c r="C30" s="4" t="s">
         <v>382</v>
       </c>
-      <c r="C30" s="4" t="s">
+      <c r="D30" s="4" t="s">
         <v>383</v>
       </c>
-      <c r="D30" s="4" t="s">
+      <c r="E30" s="4" t="s">
         <v>384</v>
       </c>
-      <c r="E30" s="4" t="s">
-        <v>385</v>
-      </c>
       <c r="F30" s="2" t="s">
-        <v>55</v>
+        <v>238</v>
       </c>
       <c r="G30" s="2" t="s">
         <v>59</v>
@@ -5205,16 +5148,16 @@
       </c>
       <c r="B31" s="5"/>
       <c r="C31" s="4" t="s">
+        <v>385</v>
+      </c>
+      <c r="D31" s="4" t="s">
         <v>386</v>
       </c>
-      <c r="D31" s="4" t="s">
+      <c r="E31" s="4" t="s">
         <v>387</v>
       </c>
-      <c r="E31" s="4" t="s">
-        <v>388</v>
-      </c>
       <c r="F31" s="2" t="s">
-        <v>55</v>
+        <v>238</v>
       </c>
       <c r="G31" s="2" t="s">
         <v>59</v>
@@ -5226,16 +5169,16 @@
       </c>
       <c r="B32" s="5"/>
       <c r="C32" s="4" t="s">
+        <v>388</v>
+      </c>
+      <c r="D32" s="4" t="s">
         <v>389</v>
       </c>
-      <c r="D32" s="4" t="s">
+      <c r="E32" s="4" t="s">
         <v>390</v>
       </c>
-      <c r="E32" s="4" t="s">
-        <v>391</v>
-      </c>
       <c r="F32" s="2" t="s">
-        <v>55</v>
+        <v>238</v>
       </c>
       <c r="G32" s="2" t="s">
         <v>59</v>
@@ -5247,16 +5190,16 @@
       </c>
       <c r="B33" s="5"/>
       <c r="C33" s="4" t="s">
+        <v>391</v>
+      </c>
+      <c r="D33" s="4" t="s">
         <v>392</v>
       </c>
-      <c r="D33" s="4" t="s">
+      <c r="E33" s="4" t="s">
         <v>393</v>
       </c>
-      <c r="E33" s="4" t="s">
-        <v>394</v>
-      </c>
       <c r="F33" s="2" t="s">
-        <v>55</v>
+        <v>238</v>
       </c>
       <c r="G33" s="2" t="s">
         <v>59</v>
@@ -5268,16 +5211,16 @@
       </c>
       <c r="B34" s="5"/>
       <c r="C34" s="4" t="s">
+        <v>394</v>
+      </c>
+      <c r="D34" s="4" t="s">
         <v>395</v>
       </c>
-      <c r="D34" s="4" t="s">
+      <c r="E34" s="4" t="s">
         <v>396</v>
       </c>
-      <c r="E34" s="4" t="s">
-        <v>397</v>
-      </c>
       <c r="F34" s="2" t="s">
-        <v>55</v>
+        <v>238</v>
       </c>
       <c r="G34" s="2" t="s">
         <v>59</v>
@@ -5289,16 +5232,16 @@
       </c>
       <c r="B35" s="5"/>
       <c r="C35" s="4" t="s">
+        <v>397</v>
+      </c>
+      <c r="D35" s="4" t="s">
         <v>398</v>
       </c>
-      <c r="D35" s="4" t="s">
+      <c r="E35" s="4" t="s">
         <v>399</v>
       </c>
-      <c r="E35" s="4" t="s">
-        <v>400</v>
-      </c>
       <c r="F35" s="2" t="s">
-        <v>55</v>
+        <v>238</v>
       </c>
       <c r="G35" s="2" t="s">
         <v>59</v>
@@ -5310,16 +5253,16 @@
       </c>
       <c r="B36" s="6"/>
       <c r="C36" s="4" t="s">
+        <v>400</v>
+      </c>
+      <c r="D36" s="4" t="s">
         <v>401</v>
       </c>
-      <c r="D36" s="4" t="s">
+      <c r="E36" s="4" t="s">
         <v>402</v>
       </c>
-      <c r="E36" s="4" t="s">
-        <v>403</v>
-      </c>
       <c r="F36" s="2" t="s">
-        <v>55</v>
+        <v>238</v>
       </c>
       <c r="G36" s="2" t="s">
         <v>59</v>
